--- a/content/Question Bank/Coding Questions/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - Coding Questions.xlsx
@@ -634,13 +634,16 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>A weather display board shows temperatures in both Celsius and Fahrenheit. Write a program that reads a temperature in Celsius and prints the equivalent temperature in Fahrenheit.
+          <t>The weather display board near the college gate shows the day's temperature, but exchange students keep asking what it means in Fahrenheit. The maintenance team decides the board should show both units side by side.
+Write a program that reads the temperature in Celsius as a decimal (`float`) number and converts it using the formula Fahrenheit = Celsius x 9/5 + 32. Print one line in the form `&lt;celsius&gt;C is &lt;fahrenheit&gt;F`, where both values are the decimal numbers your program worked with.
 ### Input Format
 - Line 1: Temperature in Celsius
 ### Output Format
 ```
-&lt;celsius&gt;C is &lt;fahrenheit&gt;F
-```
+0.0C is 32.0F
+```
+### Example Walkthrough
+In the sample, the input is 0. Read as a decimal number it becomes 0.0, and the conversion gives 0.0 x 9/5 + 32 = 32.0. So the program prints `0.0C is 32.0F`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -785,13 +788,16 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>A signup form stores a user's age as plain text, but the loyalty system needs it as a number to add bonus points. Write a program that reads the age as text, converts it to a whole number, adds 5 bonus points, and prints the new value.
+          <t>When Meena signed up on a shopping app, the form saved her age as plain text - just characters, not something you can do maths with. The loyalty system now wants to add 5 bonus points to that number to set her starting score, so the text must first be turned into a real number.
+Write a program that reads the age, converts it from text to a whole number (integer), adds 5, and prints the result in the form `New Value: &lt;new_value&gt;`.
 ### Input Format
 - Line 1: Age (entered as text)
 ### Output Format
 ```
-New Value: &lt;new_value&gt;
-```
+New Value: 25
+```
+### Example Walkthrough
+In the sample, the input is the text `20`. Converting it to an integer gives the number 20, and adding 5 gives 25. The program therefore prints `New Value: 25`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -937,14 +943,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>A cinema counter needs to calculate the total bill for a group buying tickets. Write a program that reads the price of one ticket and the number of tickets, then prints the total amount payable.
+          <t>Three friends reach the cinema just in time for the evening show, and the person at the counter needs the group's total in one go. The billing screen simply multiplies the ticket price by the number of tickets.
+Write a program that reads the price of one ticket (a decimal number) and the number of tickets (a whole number), multiplies them, and prints the total in the form `Total: Rs.&lt;total&gt;`.
 ### Input Format
 - Line 1: Price per ticket
 - Line 2: Number of tickets
 ### Output Format
 ```
-Total: Rs.&lt;total&gt;
-```
+Total: Rs.450.0
+```
+### Example Walkthrough
+In the sample, the price is 150 and the count is 3. Because the price is read as a decimal number, 150 x 3 gives 450.0, and the program prints `Total: Rs.450.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1097,13 +1106,16 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>An auto rickshaw charges a fixed base fare plus a rate per kilometre travelled. Write a program that reads the distance travelled in kilometres and prints the total fare, given a base fare of 20 and a rate of 10 per kilometre.
+          <t>Priya takes an auto rickshaw from the railway station to her college. The meter follows a simple rule: a fixed base fare of Rs.20 the moment you sit down, plus Rs.10 for every kilometre travelled.
+Write a program that reads the distance in kilometres and prints the total fare - the base fare of 20 plus 10 times the distance - in the form `Fare: Rs.&lt;fare&gt;`.
 ### Input Format
 - Line 1: Distance in kilometres
 ### Output Format
 ```
-Fare: Rs.&lt;fare&gt;
-```
+Fare: Rs.70.0
+```
+### Example Walkthrough
+In the sample, the distance is 5 km. The distance part of the fare is 10 x 5 = 50, and adding the base fare of 20 gives 70.0 (a decimal number, since the distance is read as one). The program prints `Fare: Rs.70.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1248,14 +1260,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>A fitness app calculates a member's Body Mass Index (BMI) using their weight and height. Write a program that reads a person's weight in kilograms and height in metres, then prints their BMI using the formula weight divided by height squared.
+          <t>A campus fitness app builds a health profile for every member, and the first number it computes is the Body Mass Index (BMI). BMI is simply a person's weight divided by the square of their height - that is, the height multiplied by itself.
+Write a program that reads the weight in kilograms and the height in metres (both decimal numbers) and prints the BMI in the form `BMI: &lt;bmi&gt;`, without any rounding.
 ### Input Format
 - Line 1: Weight in kilograms
 - Line 2: Height in metres
 ### Output Format
 ```
-BMI: &lt;bmi&gt;
-```
+BMI: 22.857142857142858
+```
+### Example Walkthrough
+In the sample, the weight is 70 and the height is 1.75. Squaring the height gives 1.75 x 1.75 = 3.0625, and dividing 70 by 3.0625 gives 22.857142857142858. The program prints this full value: `BMI: 22.857142857142858`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1408,14 +1423,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>A travel desk converts foreign currency to Indian Rupees for customers using the day's exchange rate. Write a program that reads an amount in US Dollars and the current exchange rate, then prints the equivalent amount in Rupees.
+          <t>Rahul's cousin in the US has sent him some dollars for his semester expenses, and the travel desk near campus converts them at the day's exchange rate. The clerk types in the dollar amount and the rate, and the screen shows the rupee value.
+Write a program that reads the amount in US Dollars and the exchange rate (rupees per dollar), multiplies them, and prints the result in the form `Amount in INR: &lt;inr&gt;`.
 ### Input Format
 - Line 1: Amount in US Dollars
 - Line 2: Exchange rate (INR per USD)
 ### Output Format
 ```
-Amount in INR: &lt;inr&gt;
-```
+Amount in INR: 8300.0
+```
+### Example Walkthrough
+In the sample, the amount is 100 dollars and the rate is 83 rupees per dollar. Multiplying gives 100 x 83 = 8300.0 (a decimal number, since the inputs are read as decimals). The program prints `Amount in INR: 8300.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1568,15 +1586,18 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>An online store shows the discount amount and the final price during a sale. Write a program that reads the original price and the discount percentage, then prints the discount amount and the final price after the discount is applied.
+          <t>The festival sale is live on an online store, and shoppers want to see exactly how much they save before paying. For each product, the page shows the discount amount and the price after the discount.
+Write a program that reads the original price and the discount percentage. The discount amount is price x percentage / 100, and the final price is the original price minus that discount. Print the two results on two lines in the form shown below.
 ### Input Format
 - Line 1: Original price
 - Line 2: Discount percentage
 ### Output Format
 ```
-Discount: &lt;discount&gt;
-Final Price: &lt;final_price&gt;
-```
+Discount: 200.0
+Final Price: 800.0
+```
+### Example Walkthrough
+In the sample, the price is 1000 and the discount is 20 percent. The discount amount is 1000 x 20 / 100 = 200.0, and the final price is 1000 - 200.0 = 800.0. The program prints `Discount: 200.0` on the first line and `Final Price: 800.0` on the second.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1738,16 +1759,19 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>An electricity provider bills a fixed monthly charge plus a per-unit rate for the power consumed. Write a program that reads the units consumed, the rate per unit, and the fixed monthly charge, then prints the variable charge and the total bill, each rounded to two decimal places.
+          <t>The monthly electricity bill for Anil's house has two parts: a fixed charge that stays the same every month, and a variable charge that depends on how many units of power were used. The provider's billing software prints both the variable charge and the grand total.
+Write a program that reads the units consumed, the rate per unit, and the fixed monthly charge. Compute the variable charge as units x rate, add the fixed charge to get the total bill, and print both values rounded to exactly two decimal places.
 ### Input Format
 - Line 1: Units consumed
 - Line 2: Rate per unit
 - Line 3: Fixed monthly charge
 ### Output Format
 ```
-Variable Charge: &lt;variable_charge&gt;
-Total Bill: &lt;total_bill&gt;
-```
+Variable Charge: 975.00
+Total Bill: 1075.00
+```
+### Example Walkthrough
+In the sample, 150 units at 6.5 per unit give a variable charge of 150 x 6.5 = 975, and adding the fixed charge of 100 gives a total of 1075. Shown with two decimal places, the program prints `Variable Charge: 975.00` and `Total Bill: 1075.00`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1917,17 +1941,20 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A group of friends at a restaurant wants the bill, the tip, and the per-person share calculated together so everyone can pay their exact part. Write a program that reads the bill amount, the tip percentage, and the number of people, then prints the tip amount, the total amount including tip, and the amount each person should pay, each rounded to two decimal places.
+          <t>Four friends celebrate the end of exams at a restaurant, and when the bill arrives they want to split it fairly - including the tip. One of them opens a bill-splitting app that works out the tip, the new total, and each person's share.
+Write a program that reads the bill amount, the tip percentage, and the number of people. The tip is bill x percentage / 100, the total is the bill plus the tip, and the per-person share is the total divided by the number of people. Print all three values, each rounded to exactly two decimal places.
 ### Input Format
 - Line 1: Bill amount
 - Line 2: Tip percentage
 - Line 3: Number of people
 ### Output Format
 ```
-Tip: &lt;tip&gt;
-Total: &lt;total&gt;
-Per Person: &lt;per_person&gt;
-```
+Tip: 120.00
+Total: 1320.00
+Per Person: 330.00
+```
+### Example Walkthrough
+In the sample, the bill is 1200 with a 10 percent tip, split among 4 people. The tip is 1200 x 10 / 100 = 120, the total is 1200 + 120 = 1320, and each person pays 1320 / 4 = 330. With two decimal places, the program prints `Tip: 120.00`, `Total: 1320.00`, and `Per Person: 330.00`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -2106,14 +2133,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>A billing system stores a price as text with decimals, but needs a rounded-down whole-rupee version for a quick summary label. Write a program that reads a price as text, converts it to a float, converts that float to an integer (truncating the decimal part), then prints both the original float value and the truncated integer value with a unit label, demonstrating the conversion chain from text to float to integer.
+          <t>A billing system receives a product's price as text from an online form - for example `199.99` - but the invoice needs a quick summary label showing just the whole-rupee part, with the paise chopped off. Getting there takes a chain of conversions: text to decimal number, then decimal number to whole number.
+Write a program that reads the price as text, converts it to a `float`, then converts that `float` to an integer (which simply drops everything after the decimal point - no rounding). Print the float value and then the integer value on two labelled lines as shown below.
 ### Input Format
 - Line 1: Price (entered as text, may contain decimals)
 ### Output Format
 ```
-As Float: &lt;float_value&gt;
-As Whole Rupees: &lt;int_value&gt;
-```
+As Float: 199.99
+As Whole Rupees: 199
+```
+### Example Walkthrough
+In the sample, the input text is `199.99`. Converting it to a `float` gives 199.99, and converting that `float` to an integer drops the .99, leaving 199. The program prints `As Float: 199.99` and then `As Whole Rupees: 199`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - Coding Questions.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,149 +426,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>difficulty</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>bloomTaxonomy</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subjects</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>topics</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>subTopics</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>companies</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>codingType</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>supportAllLanguages</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>enablePartialScore</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ignoreCase</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>testcase1_input</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>testcase1_output</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>testcase2_input</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>testcase2_output</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>testcase3_input</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>testcase3_output</t>
         </is>
@@ -610,29 +585,29 @@
           <t>testcase7_output</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>preloadCode_python</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>solution_python</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>hints</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Temperature Converter</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>The weather display board near the college gate shows the day's temperature, but exchange students keep asking what it means in Fahrenheit. The maintenance team decides the board should show both units side by side.
 Write a program that reads the temperature in Celsius as a decimal (`float`) number and converts it using the formula Fahrenheit = Celsius x 9/5 + 32. Print one line in the form `&lt;celsius&gt;C is &lt;fahrenheit&gt;F`, where both values are the decimal numbers your program worked with.
@@ -649,83 +624,89 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" s="2" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P2" s="2" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" s="2" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.0C is 32.0F</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>37.0C is 98.6F</t>
         </is>
       </c>
-      <c r="V2" s="3" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="W2" s="3" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>100.0C is 212.0F</t>
         </is>
@@ -770,23 +751,21 @@
           <t>1000.0C is 1832.0F</t>
         </is>
       </c>
-      <c r="AF2" s="3" t="n"/>
-      <c r="AG2" s="3" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>celsius = float(input())
 fahrenheit = celsius * 9 / 5 + 32
 print(f"{celsius}C is {fahrenheit}F")</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - String to Number Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>When Meena signed up on a shopping app, the form saved her age as plain text - just characters, not something you can do maths with. The loyalty system now wants to add 5 bonus points to that number to set her starting score, so the text must first be turned into a real number.
 Write a program that reads the age, converts it from text to a whole number (integer), adds 5, and prints the result in the form `New Value: &lt;new_value&gt;`.
@@ -803,83 +782,89 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>data-types</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>type-conversion</t>
         </is>
       </c>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" s="2" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P3" s="2" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" s="2" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>New Value: 25</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>New Value: 40</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>New Value: 23</t>
         </is>
@@ -924,8 +909,7 @@
           <t>New Value: 10004</t>
         </is>
       </c>
-      <c r="AF3" s="3" t="n"/>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>age_text = input()
 age = int(age_text)
@@ -933,15 +917,14 @@
 print("New Value:", new_value)</t>
         </is>
       </c>
-      <c r="AH3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Movie Ticket Total</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Three friends reach the cinema just in time for the evening show, and the person at the counter needs the group's total in one go. The billing screen simply multiplies the ticket price by the number of tickets.
 Write a program that reads the price of one ticket (a decimal number) and the number of tickets (a whole number), multiplies them, and prints the total in the form `Total: Rs.&lt;total&gt;`.
@@ -959,86 +942,92 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" s="2" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P4" s="2" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q4" s="2" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>150
 3</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Total: Rs.450.0</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>220.5
 2</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Total: Rs.441.0</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>99
 1</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Total: Rs.99.0</t>
         </is>
@@ -1087,8 +1076,7 @@
           <t>Total: Rs.100000.0</t>
         </is>
       </c>
-      <c r="AF4" s="3" t="n"/>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>price = float(input())
 count = int(input())
@@ -1096,15 +1084,14 @@
 print("Total: Rs.", total, sep="")</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Auto Rickshaw Fare</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Priya takes an auto rickshaw from the railway station to her college. The meter follows a simple rule: a fixed base fare of Rs.20 the moment you sit down, plus Rs.10 for every kilometre travelled.
 Write a program that reads the distance in kilometres and prints the total fare - the base fare of 20 plus 10 times the distance - in the form `Fare: Rs.&lt;fare&gt;`.
@@ -1121,83 +1108,89 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" s="2" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P5" s="2" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q5" s="2" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Fare: Rs.70.0</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Fare: Rs.45.0</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Fare: Rs.120.0</t>
         </is>
@@ -1242,23 +1235,21 @@
           <t>Fare: Rs.1020.0</t>
         </is>
       </c>
-      <c r="AF5" s="3" t="n"/>
-      <c r="AG5" s="3" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>distance = float(input())
 fare = 20 + distance * 10
 print("Fare: Rs.", fare, sep="")</t>
         </is>
       </c>
-      <c r="AH5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - BMI Calculator</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>A campus fitness app builds a health profile for every member, and the first number it computes is the Body Mass Index (BMI). BMI is simply a person's weight divided by the square of their height - that is, the height multiplied by itself.
 Write a program that reads the weight in kilograms and the height in metres (both decimal numbers) and prints the BMI in the form `BMI: &lt;bmi&gt;`, without any rounding.
@@ -1276,86 +1267,92 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" s="2" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P6" s="2" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q6" s="2" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>70
 1.75</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>BMI: 22.857142857142858</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>55
 1.6</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>BMI: 21.484374999999996</t>
         </is>
       </c>
-      <c r="V6" s="3" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>90
 1.8</t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>BMI: 27.777777777777775</t>
         </is>
@@ -1404,8 +1401,7 @@
           <t>BMI: 4.0</t>
         </is>
       </c>
-      <c r="AF6" s="3" t="n"/>
-      <c r="AG6" s="3" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>weight = float(input())
 height = float(input())
@@ -1413,15 +1409,14 @@
 print("BMI:", bmi)</t>
         </is>
       </c>
-      <c r="AH6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Currency Converter</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Rahul's cousin in the US has sent him some dollars for his semester expenses, and the travel desk near campus converts them at the day's exchange rate. The clerk types in the dollar amount and the rate, and the screen shows the rupee value.
 Write a program that reads the amount in US Dollars and the exchange rate (rupees per dollar), multiplies them, and prints the result in the form `Amount in INR: &lt;inr&gt;`.
@@ -1439,86 +1434,92 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" s="2" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P7" s="2" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q7" s="2" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>100
 83</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Amount in INR: 8300.0</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>50
 83.5</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Amount in INR: 4175.0</t>
         </is>
       </c>
-      <c r="V7" s="3" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>250
 82.75</t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Amount in INR: 20687.5</t>
         </is>
@@ -1567,8 +1568,7 @@
           <t>Amount in INR: 500000.0</t>
         </is>
       </c>
-      <c r="AF7" s="3" t="n"/>
-      <c r="AG7" s="3" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>usd_amount = float(input())
 exchange_rate = float(input())
@@ -1576,15 +1576,14 @@
 print("Amount in INR:", inr)</t>
         </is>
       </c>
-      <c r="AH7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Discount Price Calculator</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>The festival sale is live on an online store, and shoppers want to see exactly how much they save before paying. For each product, the page shows the discount amount and the price after the discount.
 Write a program that reads the original price and the discount percentage. The discount amount is price x percentage / 100, and the final price is the original price minus that discount. Print the two results on two lines in the form shown below.
@@ -1603,88 +1602,94 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" s="2" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P8" s="2" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q8" s="2" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>1000
 20</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Discount: 200.0
 Final Price: 800.0</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>500
 10</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Discount: 50.0
 Final Price: 450.0</t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1499
 15</t>
         </is>
       </c>
-      <c r="W8" s="3" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Discount: 224.85
 Final Price: 1274.15</t>
@@ -1738,8 +1743,7 @@
 Final Price: 666.6933329999999</t>
         </is>
       </c>
-      <c r="AF8" s="3" t="n"/>
-      <c r="AG8" s="3" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>price = float(input())
 discount_percent = float(input())
@@ -1749,15 +1753,14 @@
 print("Final Price:", final_price)</t>
         </is>
       </c>
-      <c r="AH8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Electricity Bill Calculator</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>The monthly electricity bill for Anil's house has two parts: a fixed charge that stays the same every month, and a variable charge that depends on how many units of power were used. The provider's billing software prints both the variable charge and the grand total.
 Write a program that reads the units consumed, the rate per unit, and the fixed monthly charge. Compute the variable charge as units x rate, add the fixed charge to get the total bill, and print both values rounded to exactly two decimal places.
@@ -1777,91 +1780,97 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" s="2" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P9" s="2" t="b">
+      <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="Q9" s="2" t="b">
+      <c r="Q9" t="b">
         <v>1</v>
       </c>
-      <c r="R9" s="3" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>150
 6.5
 100</t>
         </is>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Variable Charge: 975.00
 Total Bill: 1075.00</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>320.5
 7
 150</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Variable Charge: 2243.50
 Total Bill: 2393.50</t>
         </is>
       </c>
-      <c r="V9" s="3" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0
 6.5
 100</t>
         </is>
       </c>
-      <c r="W9" s="3" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Variable Charge: 0.00
 Total Bill: 100.00</t>
@@ -1919,8 +1928,7 @@
 Total Bill: 4450.00</t>
         </is>
       </c>
-      <c r="AF9" s="3" t="n"/>
-      <c r="AG9" s="3" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>units = float(input())
 rate_per_unit = float(input())
@@ -1931,15 +1939,508 @@
 print(f"Total Bill: {total_bill:.2f}")</t>
         </is>
       </c>
-      <c r="AH9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - GST Bill Total</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for GST Bill Total. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Amount
+### Output Format
+```
+118.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>arithmetic-operators</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>250.5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>295.59</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>999.99</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1179.99</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1234.56</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1456.78</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>a=float(input())
+print(round(a*1.18,2))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Minutes Split</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Minutes Split. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Minutes
+### Output Format
+```
+2 hours 5 minutes
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>arithmetic-operators</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2 hours 5 minutes</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1 hours 0 minutes</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0 hours 59 minutes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0 hours 0 minutes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>24 hours 0 minutes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>16 hours 41 minutes</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0 hours 7 minutes</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>m=int(input())
+print(m//60, "hours", m%60, "minutes")</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Restaurant Tip Splitter</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Four friends celebrate the end of exams at a restaurant, and when the bill arrives they want to split it fairly - including the tip. One of them opens a bill-splitting app that works out the tip, the new total, and each person's share.
 Write a program that reads the bill amount, the tip percentage, and the number of people. The tip is bill x percentage / 100, the total is the bill plus the tip, and the per-person share is the total divided by the number of people. Print all three values, each rounded to exactly two decimal places.
@@ -1960,157 +2461,162 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" s="2" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" s="2" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q10" s="2" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>1200
 10
 4</t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Tip: 120.00
 Total: 1320.00
 Per Person: 330.00</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>850.5
 15
 3</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Tip: 127.58
 Total: 978.08
 Per Person: 326.03</t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>500
 0
 5</t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Tip: 0.00
 Total: 500.00
 Per Person: 100.00</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0
 10
 1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Tip: 0.00
 Total: 0.00
 Per Person: 0.00</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>100
 0
 1</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Tip: 0.00
 Total: 100.00
 Per Person: 100.00</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>100
 10
 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Tip: 10.00
 Total: 110.00
 Per Person: 110.00</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>999.99
 33.33
 7</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Tip: 333.30
 Total: 1333.29
 Per Person: 190.47</t>
         </is>
       </c>
-      <c r="AF10" s="3" t="n"/>
-      <c r="AG10" s="3" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>bill_amount = float(input())
 tip_percent = float(input())
@@ -2123,15 +2629,14 @@
 print(f"Per Person: {per_person:.2f}")</t>
         </is>
       </c>
-      <c r="AH10" s="2" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Type Conversion Chain</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>A billing system receives a product's price as text from an online form - for example `199.99` - but the invoice needs a quick summary label showing just the whole-rupee part, with the paise chopped off. Getting there takes a chain of conversions: text to decimal number, then decimal number to whole number.
 Write a program that reads the price as text, converts it to a `float`, then converts that `float` to an integer (which simply drops everything after the decimal point - no rounding). Print the float value and then the integer value on two labelled lines as shown below.
@@ -2149,136 +2654,141 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>data-types</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>type-conversion</t>
         </is>
       </c>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" s="2" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" s="2" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q11" s="2" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>199.99</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>As Float: 199.99
 As Whole Rupees: 199</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>50.5</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>As Float: 50.5
 As Whole Rupees: 50</t>
         </is>
       </c>
-      <c r="V11" s="3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="W11" s="3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>As Float: 1000.0
 As Whole Rupees: 1000</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>As Float: 0.0
 As Whole Rupees: 0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.001</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>As Float: 0.001
 As Whole Rupees: 0</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>-5.5</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>As Float: -5.5
 As Whole Rupees: -5</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>123456.789</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>As Float: 123456.789
 As Whole Rupees: 123456</t>
         </is>
       </c>
-      <c r="AF11" s="3" t="n"/>
-      <c r="AG11" s="3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>price_text = input()
 price_float = float(price_text)
@@ -2287,15 +2797,14 @@
 print("As Whole Rupees:", price_int)</t>
         </is>
       </c>
-      <c r="AH11" s="2" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Canteen Cookie Boxing</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>The canteen packs cookies into boxes for the evening snack counter. Write a program that reads the total number of cookies and the number of cookies per box, then prints how many full boxes can be packed and how many cookies are left over.
 ### Input Format
@@ -2303,151 +2812,158 @@
 - Line 2: Cookies per box
 ### Output Format
 ```
-Boxes: &lt;boxes&gt;
-Leftover: &lt;leftover&gt;
+Boxes: 8
+Leftover: 2
 ```
+### Example Walkthrough
+In the sample, the total is `50` cookies with `6` per box. Dividing gives `50 // 6 = 8` full boxes, with `50 % 6 = 2` cookies left over. The program prints `Boxes: 8` and `Leftover: 2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" s="2" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" s="2" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q12" s="2" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>50
 6</t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Boxes: 8
 Leftover: 2</t>
         </is>
       </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>100
 9</t>
         </is>
       </c>
-      <c r="U12" s="3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Boxes: 11
 Leftover: 1</t>
         </is>
       </c>
-      <c r="V12" s="3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>23
 5</t>
         </is>
       </c>
-      <c r="W12" s="3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Boxes: 4
 Leftover: 3</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0
 6</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Boxes: 0
 Leftover: 0</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>6
 6</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Boxes: 1
 Leftover: 0</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>1
 3</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Boxes: 0
 Leftover: 1</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>1000000
 7</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Boxes: 142857
 Leftover: 1</t>
         </is>
       </c>
-      <c r="AF12" s="3" t="n"/>
-      <c r="AG12" s="3" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>cookies = int(input())
 per_box = int(input())
@@ -2457,15 +2973,14 @@
 print("Leftover:", leftover)</t>
         </is>
       </c>
-      <c r="AH12" s="2" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Rectangular Garden Area</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>A gardener wants to know the area of a rectangular plot before ordering grass turf. Write a program that reads the length and width of the plot in metres and prints its area.
 ### Input Format
@@ -2473,143 +2988,150 @@
 - Line 2: Width in metres
 ### Output Format
 ```
-Area: &lt;area&gt; sq.m
+Area: 96.0 sq.m
 ```
+### Example Walkthrough
+In the sample, the length is `12` and the width is `8`, both read as decimal numbers. Multiplying gives `12.0 x 8.0 = 96.0`, so the program prints `Area: 96.0 sq.m`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" s="2" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" s="2" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q13" s="2" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>10
 5</t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Area: 50.0 sq.m</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>12.5
 4</t>
         </is>
       </c>
-      <c r="U13" s="3" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Area: 50.0 sq.m</t>
         </is>
       </c>
-      <c r="V13" s="3" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>7
 7</t>
         </is>
       </c>
-      <c r="W13" s="3" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Area: 49.0 sq.m</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Area: 0.0 sq.m</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Area: 1.0 sq.m</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.5
 0.5</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Area: 0.25 sq.m</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>1000
 1000</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Area: 1000000.0 sq.m</t>
         </is>
       </c>
-      <c r="AF13" s="3" t="n"/>
-      <c r="AG13" s="3" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>length = float(input())
 width = float(input())
@@ -2617,15 +3139,14 @@
 print("Area:", area, "sq.m")</t>
         </is>
       </c>
-      <c r="AH13" s="2" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Full Name Tag</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>An event registration desk prints a name tag for every attendee. Write a program that reads a first name and a last name, then prints the full name joined with a space.
 ### Input Format
@@ -2633,143 +3154,150 @@
 - Line 2: Last name
 ### Output Format
 ```
-Name Tag: &lt;First&gt; &lt;Last&gt;
+Name Tag: Devika Rao
 ```
+### Example Walkthrough
+In the sample, the inputs are `Devika` and `Rao`. Joining them with a space gives `Devika Rao`, so the program prints `Name Tag: Devika Rao`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>arithmetic-operators</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>strings-and-booleans</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" s="2" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" s="2" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q14" s="2" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R14" s="3" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Asha
 Verma</t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Name Tag: Asha Verma</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Kabir
 Khan</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Name Tag: Kabir Khan</t>
         </is>
       </c>
-      <c r="V14" s="3" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Meera
 Iyer</t>
         </is>
       </c>
-      <c r="W14" s="3" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Name Tag: Meera Iyer</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>A
 B</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Name Tag: A B</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Jean-Luc
 O'Brien</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Name Tag: Jean-Luc O'Brien</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>X
 Y</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Name Tag: X Y</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Ravi
 Kumar</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Name Tag: Ravi Kumar</t>
         </is>
       </c>
-      <c r="AF14" s="3" t="n"/>
-      <c r="AG14" s="3" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>first = input()
 last = input()
@@ -2777,15 +3305,14 @@
 print("Name Tag:", full_name)</t>
         </is>
       </c>
-      <c r="AH14" s="2" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Average of Two Tests</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>A teacher wants the average score across two unit tests for quick reporting. Write a program that reads two test scores and prints their average.
 ### Input Format
@@ -2793,143 +3320,150 @@
 - Line 2: Score in test 2
 ### Output Format
 ```
-Average: &lt;average&gt;
+Average: 86.0
 ```
+### Example Walkthrough
+In the sample, the two scores are `82` and `90`. Their average is `(82.0 + 90.0) / 2 = 86.0`, so the program prints `Average: 86.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" s="2" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" s="2" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q15" s="2" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R15" s="3" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>80
 90</t>
         </is>
       </c>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Average: 85.0</t>
         </is>
       </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>45
 55</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Average: 50.0</t>
         </is>
       </c>
-      <c r="V15" s="3" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>72
 68</t>
         </is>
       </c>
-      <c r="W15" s="3" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Average: 70.0</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Average: 0.0</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>100
 100</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Average: 100.0</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>-10
 10</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Average: 0.0</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>-20
 -30</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Average: -25.0</t>
         </is>
       </c>
-      <c r="AF15" s="3" t="n"/>
-      <c r="AG15" s="3" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>score1 = float(input())
 score2 = float(input())
@@ -2937,317 +3471,849 @@
 print("Average:", average)</t>
         </is>
       </c>
-      <c r="AH15" s="2" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Gym Membership Days</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>A gym wants to convert a membership duration given in weeks into the equivalent number of days for its records. Write a program that reads the number of weeks and prints the total number of days.
 ### Input Format
 - Line 1: Number of weeks
 ### Output Format
 ```
-Total Days: &lt;days&gt;
+Total Days: 42
 ```
+### Example Walkthrough
+In the sample, the duration is `6` weeks. Multiplying by 7 gives `6 x 7 = 42` days, so the program prints `Total Days: 42`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" s="2" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" s="2" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q16" s="2" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R16" s="3" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S16" s="3" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Total Days: 28</t>
         </is>
       </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Total Days: 84</t>
         </is>
       </c>
-      <c r="V16" s="3" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W16" s="3" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Total Days: 7</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Total Days: 0</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Total Days: -7</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Total Days: 364</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Total Days: 7000</t>
         </is>
       </c>
-      <c r="AF16" s="3" t="n"/>
-      <c r="AG16" s="3" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>weeks = int(input())
 days = weeks * 7
 print("Total Days:", days)</t>
         </is>
       </c>
-      <c r="AH16" s="2" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Pass Mark Check</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>An online quiz platform wants to display whether a student's score meets the passing mark of 40, without yet branching the program's behaviour. Write a program that reads a score and prints whether it is greater than or equal to 40.
 ### Input Format
 - Line 1: Score
 ### Output Format
 ```
-Pass Status: &lt;True/False&gt;
+Pass Status: True
 ```
+### Example Walkthrough
+In the sample, the score is `55`. Since `55 &gt;= 40` is `True`, the program prints `Pass Status: True`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>arithmetic-operators</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>comparison-and-logical-operators</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" s="2" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" s="2" t="b">
+      <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="Q17" s="2" t="b">
+      <c r="Q9" t="b">
         <v>1</v>
       </c>
-      <c r="R17" s="3" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Pass Status: True</t>
         </is>
       </c>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Pass Status: False</t>
         </is>
       </c>
-      <c r="V17" s="3" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="W17" s="3" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Pass Status: True</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Pass Status: False</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>39.99</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Pass Status: False</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>40.01</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>Pass Status: True</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>Pass Status: False</t>
         </is>
       </c>
-      <c r="AF17" s="3" t="n"/>
-      <c r="AG17" s="3" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>score = float(input())
 is_pass = score &gt;= 40
 print("Pass Status:", is_pass)</t>
         </is>
       </c>
-      <c r="AH17" s="2" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Name Age Line</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Name Age Line. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Name
+- Line 2: Age
+### Output Format
+```
+Asha is 19 years old
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>input-and-output</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Asha
+19</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Asha is 19 years old</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Rohan
+20</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rohan is 20 years old</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Meena
+18</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Meena is 18 years old</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Kabir
+21</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Kabir is 21 years old</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Zoya
+17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Zoya is 17 years old</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Dev
+22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Dev is 22 years old</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>S
+1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>S is 1 years old</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>name=input()
+age=int(input())
+print(f"{name} is {age} years old")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Remainder Counter</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Remainder Counter. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Items
+- Line 2: Group size
+### Output Format
+```
+Full groups: 3
+Left over: 2
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>arithmetic-operators</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>17
+5</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Full groups: 3
+Left over: 2</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>10
+2</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Full groups: 5
+Left over: 0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>9
+4</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Full groups: 2
+Left over: 1</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0
+3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Full groups: 0
+Left over: 0</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>100
+10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Full groups: 10
+Left over: 0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>99
+8</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Full groups: 12
+Left over: 3</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>7
+9</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Full groups: 0
+Left over: 7</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>items=int(input())
+size=int(input())
+print("Full groups:", items//size)
+print("Left over:", items%size)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Canteen Bill Calculator</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>The canteen counter needs to print a short bill that includes tax. Write a program that reads an item's price, the quantity ordered, and the tax percentage, then prints the subtotal, the tax amount, and the final total.
 ### Input Format
@@ -3256,166 +4322,173 @@
 - Line 3: Tax percentage
 ### Output Format
 ```
-Subtotal: &lt;subtotal&gt;
-Tax: &lt;tax&gt;
-Total: &lt;total&gt;
+Subtotal: 150.0
+Tax: 7.5
+Total: 157.5
 ```
+### Example Walkthrough
+In the sample, the price is `50`, the quantity is `3`, and the tax is `5` percent. The subtotal is `50.0 x 3 = 150.0`, the tax is `150.0 x 5 / 100 = 7.5`, and the total is `150.0 + 7.5 = 157.5`. The program prints `Subtotal: 150.0`, `Tax: 7.5`, and `Total: 157.5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" s="2" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" s="2" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q18" s="2" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R18" s="3" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>50
 2
 5</t>
         </is>
       </c>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Subtotal: 100.0
 Tax: 5.0
 Total: 105.0</t>
         </is>
       </c>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>120
 1
 10</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Subtotal: 120.0
 Tax: 12.0
 Total: 132.0</t>
         </is>
       </c>
-      <c r="V18" s="3" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>75.5
 3
 8</t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Subtotal: 226.5
 Tax: 18.12
 Total: 244.62</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0
 1
 0</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Subtotal: 0.0
 Tax: 0.0
 Total: 0.0</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>10
 0
 5</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Subtotal: 0.0
 Tax: 0.0
 Total: 0.0</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>50
 2
 0</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Subtotal: 100.0
 Tax: 0.0
 Total: 100.0</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>33.33
 3
 100</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Subtotal: 99.99
 Tax: 99.99
 Total: 199.98</t>
         </is>
       </c>
-      <c r="AF18" s="3" t="n"/>
-      <c r="AG18" s="3" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>price = float(input())
 quantity = int(input())
@@ -3428,15 +4501,14 @@
 print("Total:", total)</t>
         </is>
       </c>
-      <c r="AH18" s="2" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Petrol Cost Splitter</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Four friends share a car for a road trip and want to split the petrol cost evenly, keeping track of any amount that cannot be split evenly. Write a program that reads the total petrol cost and the number of friends, then prints each friend's even share and the leftover amount.
 ### Input Format
@@ -3444,151 +4516,158 @@
 - Line 2: Number of friends
 ### Output Format
 ```
-Share per person: &lt;share&gt;
-Leftover: &lt;leftover&gt;
+Share per person: 333
+Leftover: 1
 ```
+### Example Walkthrough
+In the sample, the total cost is `1000` split among `3` friends. Each friend's even share is `1000 // 3 = 333`, with `1000 % 3 = 1` left over. The program prints `Share per person: 333` and `Leftover: 1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" s="2" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" s="2" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q19" s="2" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R19" s="3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>100
 3</t>
         </is>
       </c>
-      <c r="S19" s="3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Share per person: 33
 Leftover: 1</t>
         </is>
       </c>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>250
 4</t>
         </is>
       </c>
-      <c r="U19" s="3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Share per person: 62
 Leftover: 2</t>
         </is>
       </c>
-      <c r="V19" s="3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>999
 7</t>
         </is>
       </c>
-      <c r="W19" s="3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Share per person: 142
 Leftover: 5</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Share per person: 0
 Leftover: 0</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Share per person: 1
 Leftover: 0</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>100
 1</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Share per person: 100
 Leftover: 0</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>1000000
 13</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Share per person: 76923
 Leftover: 1</t>
         </is>
       </c>
-      <c r="AF19" s="3" t="n"/>
-      <c r="AG19" s="3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>total_cost = int(input())
 friends = int(input())
@@ -3598,15 +4677,14 @@
 print("Leftover:", leftover)</t>
         </is>
       </c>
-      <c r="AH19" s="2" t="n"/>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Exam Score Aggregator</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>A report card generator needs the total and average of three subject marks for a student. Write a program that reads three marks and prints their total and their average.
 ### Input Format
@@ -3615,158 +4693,165 @@
 - Line 3: Marks in subject 3
 ### Output Format
 ```
-Total: &lt;total&gt;
-Average: &lt;average&gt;
+Total: 255.0
+Average: 85.0
 ```
+### Example Walkthrough
+In the sample, the three marks are `80`, `85`, and `90`. Their total is `255.0` and their average is `255.0 / 3 = 85.0`, so the program prints `Total: 255.0` and `Average: 85.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" s="2" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" s="2" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q20" s="2" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R20" s="3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>80
 75
 90</t>
         </is>
       </c>
-      <c r="S20" s="3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Total: 245.0
 Average: 81.66666666666667</t>
         </is>
       </c>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>60
 65
 70</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Total: 195.0
 Average: 65.0</t>
         </is>
       </c>
-      <c r="V20" s="3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>100
 95
 98</t>
         </is>
       </c>
-      <c r="W20" s="3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Total: 293.0
 Average: 97.66666666666667</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0
 0
 0</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Total: 0.0
 Average: 0.0</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>100
 100
 100</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Total: 300.0
 Average: 100.0</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>-10
 50
 60</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Total: 100.0
 Average: 33.333333333333336</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>33
 33
 34</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Total: 100.0
 Average: 33.333333333333336</t>
         </is>
       </c>
-      <c r="AF20" s="3" t="n"/>
-      <c r="AG20" s="3" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>marks1 = float(input())
 marks2 = float(input())
@@ -3777,15 +4862,14 @@
 print("Average:", average)</t>
         </is>
       </c>
-      <c r="AH20" s="2" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Library Fine Calculator</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>The library charges a fixed late fee plus an extra amount for every day a book is overdue. Write a program that reads the number of days a book is late and the per-day fine rate, then prints the total fine, given a fixed late fee of 10.
 ### Input Format
@@ -3793,143 +4877,150 @@
 - Line 2: Fine per day
 ### Output Format
 ```
-Total Fine: &lt;total_fine&gt;
+Total Fine: 16.0
 ```
+### Example Walkthrough
+In the sample, the book is `3` days late at a rate of `2` per day. The total fine is the fixed `10` plus `3 x 2.0 = 6.0`, giving `16.0`, so the program prints `Total Fine: 16.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" s="2" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" s="2" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q21" s="2" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R21" s="3" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>5
 2</t>
         </is>
       </c>
-      <c r="S21" s="3" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Total Fine: 20.0</t>
         </is>
       </c>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0
 2</t>
         </is>
       </c>
-      <c r="U21" s="3" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Total Fine: 10.0</t>
         </is>
       </c>
-      <c r="V21" s="3" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>10
 1.5</t>
         </is>
       </c>
-      <c r="W21" s="3" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Total Fine: 25.0</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Total Fine: 10.0</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Total Fine: 10.0</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>100
 0.5</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Total Fine: 60.0</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>365
 5</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Total Fine: 1835.0</t>
         </is>
       </c>
-      <c r="AF21" s="3" t="n"/>
-      <c r="AG21" s="3" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>days_late = int(input())
 fine_per_day = float(input())
@@ -3937,15 +5028,14 @@
 print("Total Fine:", total_fine)</t>
         </is>
       </c>
-      <c r="AH21" s="2" t="n"/>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Class Average and Pass Margin</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>A teacher wants to know not just whether a student passed, but by how much they cleared (or missed) the passing mark. Write a program that reads a student's marks and the passing mark, then prints the margin by which the marks exceed the passing mark, and whether the student passed.
 ### Input Format
@@ -3953,151 +5043,158 @@
 - Line 2: Passing marks
 ### Output Format
 ```
-Margin: &lt;margin&gt;
-Passed: &lt;True/False&gt;
+Margin: 5.0
+Passed: True
 ```
+### Example Walkthrough
+In the sample, the marks are `45` against a passing mark of `40`. The margin is `45.0 - 40.0 = 5.0`, and since `45.0 &gt;= 40.0` is `True`, the program prints `Margin: 5.0` and `Passed: True`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>arithmetic-operators</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>comparison-and-logical-operators</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" s="2" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" s="2" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q22" s="2" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R22" s="3" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>55
 40</t>
         </is>
       </c>
-      <c r="S22" s="3" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Margin: 15.0
 Passed: True</t>
         </is>
       </c>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>35
 40</t>
         </is>
       </c>
-      <c r="U22" s="3" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Margin: -5.0
 Passed: False</t>
         </is>
       </c>
-      <c r="V22" s="3" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>40
 40</t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Margin: 0.0
 Passed: True</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Margin: 0.0
 Passed: True</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>-10
 0</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Margin: -10.0
 Passed: False</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>39.99
 40</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Margin: -0.00999999999999801
 Passed: False</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1000
 40</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Margin: 960.0
 Passed: True</t>
         </is>
       </c>
-      <c r="AF22" s="3" t="n"/>
-      <c r="AG22" s="3" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>marks = float(input())
 passing_marks = float(input())
@@ -4107,15 +5204,14 @@
 print("Passed:", is_pass)</t>
         </is>
       </c>
-      <c r="AH22" s="2" t="n"/>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Taxi Fare with Surge</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>A ride-hailing app applies a surge multiplier to the normal fare during peak hours. Write a program that reads the base fare, the distance travelled in kilometres, and the surge multiplier, then prints the final fare, using a rate of 12 per kilometre before the surge is applied.
 ### Input Format
@@ -4124,150 +5220,157 @@
 - Line 3: Surge multiplier
 ### Output Format
 ```
-Final Fare: &lt;final_fare&gt;
+Final Fare: 255.0
 ```
+### Example Walkthrough
+In the sample, the base fare is `50`, the distance is `10` km, and the surge multiplier is `1.5`. Before the surge, the fare is `50.0 + 10.0 x 12 = 170.0`; applying the surge gives `170.0 x 1.5 = 255.0`, so the program prints `Final Fare: 255.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" s="2" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" s="2" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q23" s="2" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R23" s="3" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>30
 5
 1.5</t>
         </is>
       </c>
-      <c r="S23" s="3" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Final Fare: 135.0</t>
         </is>
       </c>
-      <c r="T23" s="3" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>20
 10
 1</t>
         </is>
       </c>
-      <c r="U23" s="3" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Final Fare: 140.0</t>
         </is>
       </c>
-      <c r="V23" s="3" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>25
 8
 2</t>
         </is>
       </c>
-      <c r="W23" s="3" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Final Fare: 242.0</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0
 0
 1</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Final Fare: 0.0</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>10
 0
 1</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Final Fare: 10.0</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0
 5
 0</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Final Fare: 0.0</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>50
 100
 0.5</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Final Fare: 625.0</t>
         </is>
       </c>
-      <c r="AF23" s="3" t="n"/>
-      <c r="AG23" s="3" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>base_fare = float(input())
 distance_km = float(input())
@@ -4276,15 +5379,14 @@
 print("Final Fare:", final_fare)</t>
         </is>
       </c>
-      <c r="AH23" s="2" t="n"/>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Augmented Score Tracker</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>A quiz app starts a player at a base score and then adds bonus points from two separate rounds. Write a program that reads a starting score and two bonus amounts, adds each bonus to the score one at a time using the += operator, and prints the final score.
 ### Input Format
@@ -4293,150 +5395,157 @@
 - Line 3: Bonus from round 2
 ### Output Format
 ```
-Final Score: &lt;final_score&gt;
+Final Score: 135
 ```
+### Example Walkthrough
+In the sample, the starting score is `100`, with bonuses of `20` and `15`. Adding each bonus in turn with `+=` gives `100 + 20 = 120`, then `120 + 15 = 135`, so the program prints `Final Score: 135`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>arithmetic-operators</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>assignment-operators</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" s="2" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" s="2" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q24" s="2" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R24" s="3" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>10
 5
 8</t>
         </is>
       </c>
-      <c r="S24" s="3" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Final Score: 23</t>
         </is>
       </c>
-      <c r="T24" s="3" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0
 20
 30</t>
         </is>
       </c>
-      <c r="U24" s="3" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Final Score: 50</t>
         </is>
       </c>
-      <c r="V24" s="3" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>100
 -10
 5</t>
         </is>
       </c>
-      <c r="W24" s="3" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Final Score: 95</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0
 0
 0</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Final Score: 0</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>-10
 -5
 -8</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Final Score: -23</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0
 -100
 50</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Final Score: -50</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1000
 1000
 1000</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Final Score: 3000</t>
         </is>
       </c>
-      <c r="AF24" s="3" t="n"/>
-      <c r="AG24" s="3" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>score = int(input())
 bonus1 = int(input())
@@ -4446,15 +5555,698 @@
 print("Final Score:", score)</t>
         </is>
       </c>
-      <c r="AH24" s="2" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Compare Scores</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Compare Scores. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: First
+- Line 2: Second
+### Output Format
+```
+True
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>comparison-and-logical-operators</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>90
+80</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>50
+50</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>10
+20</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0
+-1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>-5
+-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>100
+99</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1
+2</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>a=int(input())
+b=int(input())
+print(a&gt;b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Discount Price</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Discount Price. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Price
+- Line 2: Discount percent
+### Output Format
+```
+90.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>arithmetic-operators</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>100
+10</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>250
+20</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>99.99
+5</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>94.99</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>500
+0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1000
+50</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>75.5
+12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>66.44</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1
+100</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>p=float(input())
+d=float(input())
+print(round(p-p*d/100,2))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Precedence Value</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Precedence Value. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: a
+- Line 2: b
+- Line 3: c
+### Output Format
+```
+14
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>operator-precedence</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2
+3
+4</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>10
+5
+2</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0
+7
+8</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-1
+3
+5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6
+0
+9</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1
+2
+3</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>100
+10
+10</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>a=int(input())
+b=int(input())
+c=int(input())
+print(a+b*c)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Hostel Mess Bill Splitter</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>The hostel mess committee collects a fixed service charge on top of the total food bill, then splits the combined amount evenly among the students, tracking any amount left over. Write a program that reads the total food bill, the number of students, and the service charge percentage, then prints the service charge, the grand total, each student's even share, and the leftover amount.
 ### Input Format
@@ -4463,75 +6255,83 @@
 - Line 3: Service charge percentage
 ### Output Format
 ```
-Service Charge: &lt;service_charge&gt;
-Grand Total: &lt;grand_total&gt;
-Share per Student: &lt;share&gt;
-Leftover: &lt;leftover&gt;
+Service Charge: 200.0
+Grand Total: 2200.0
+Share per Student: 366
+Leftover: 4
 ```
+### Example Walkthrough
+In the sample, the food bill is `2000` split among `6` students, with a `10` percent service charge. The service charge is `2000.0 x 10 / 100 = 200.0`, giving a grand total of `2200.0`. Splitting `2200` among `6` students gives a share of `366` each, with `4` left over. The program prints `Service Charge: 200.0`, `Grand Total: 2200.0`, `Share per Student: 366`, and `Leftover: 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L25" s="2" t="n"/>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" s="2" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" s="2" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q25" s="2" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R25" s="3" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>1000
 7
 5</t>
         </is>
       </c>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Service Charge: 50.0
 Grand Total: 1050.0
@@ -4539,14 +6339,14 @@
 Leftover: 0</t>
         </is>
       </c>
-      <c r="T25" s="3" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1500
 9
 10</t>
         </is>
       </c>
-      <c r="U25" s="3" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Service Charge: 150.0
 Grand Total: 1650.0
@@ -4554,14 +6354,14 @@
 Leftover: 3</t>
         </is>
       </c>
-      <c r="V25" s="3" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>799
 4
 0</t>
         </is>
       </c>
-      <c r="W25" s="3" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Service Charge: 0.0
 Grand Total: 799.0
@@ -4569,14 +6369,14 @@
 Leftover: 3</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0
 1
 0</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Service Charge: 0.0
 Grand Total: 0.0
@@ -4584,14 +6384,14 @@
 Leftover: 0</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>100
 1
 0</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Service Charge: 0.0
 Grand Total: 100.0
@@ -4599,14 +6399,14 @@
 Leftover: 0</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1
 1
 100</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Service Charge: 1.0
 Grand Total: 2.0
@@ -4614,14 +6414,14 @@
 Leftover: 0</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>999999
 11
 7</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Service Charge: 69999.93
 Grand Total: 1069998.93
@@ -4629,8 +6429,7 @@
 Leftover: 6</t>
         </is>
       </c>
-      <c r="AF25" s="3" t="n"/>
-      <c r="AG25" s="3" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>total_bill = float(input())
 students = int(input())
@@ -4645,15 +6444,14 @@
 print("Leftover:", leftover)</t>
         </is>
       </c>
-      <c r="AH25" s="2" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Cab Trip Fare Breakdown</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>A cab aggregator's invoice shows a clear breakdown of the distance fare and the waiting-time fare before the final total, formatted to two decimal places. Write a program that reads the base fare, the distance in kilometres, the waiting time in minutes, and the per-minute waiting rate, then prints the distance fare, the waiting fare, and the total fare, each rounded to two decimal places, using a distance rate of 12 per kilometre.
 ### Input Format
@@ -4663,67 +6461,75 @@
 - Line 4: Rate per minute of waiting
 ### Output Format
 ```
-Distance Fare: &lt;distance_fare&gt;
-Waiting Fare: &lt;waiting_fare&gt;
-Total Fare: &lt;total_fare&gt;
+Distance Fare: 136.00
+Waiting Fare: 10.00
+Total Fare: 146.00
 ```
+### Example Walkthrough
+In the sample, the base fare is `40`, the distance is `8` km, the waiting time is `5` minutes, and the waiting rate is `2` per minute. The distance fare is `40.0 + 8.0 x 12 = 136.0`, the waiting fare is `5.0 x 2.0 = 10.0`, and the total is `146.0`. Rounded to two decimal places, the program prints `Distance Fare: 136.00`, `Waiting Fare: 10.00`, and `Total Fare: 146.00`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" s="2" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" s="2" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q26" s="2" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R26" s="3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>20
 8
@@ -4731,14 +6537,14 @@
 2</t>
         </is>
       </c>
-      <c r="S26" s="3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Distance Fare: 116.00
 Waiting Fare: 10.00
 Total Fare: 126.00</t>
         </is>
       </c>
-      <c r="T26" s="3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>15
 12.5
@@ -4746,14 +6552,14 @@
 2</t>
         </is>
       </c>
-      <c r="U26" s="3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Distance Fare: 165.00
 Waiting Fare: 0.00
 Total Fare: 165.00</t>
         </is>
       </c>
-      <c r="V26" s="3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>25
 6.25
@@ -4761,14 +6567,14 @@
 1.5</t>
         </is>
       </c>
-      <c r="W26" s="3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Distance Fare: 100.00
 Waiting Fare: 15.00
 Total Fare: 115.00</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0
 0
@@ -4776,14 +6582,14 @@
 0</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Distance Fare: 0.00
 Waiting Fare: 0.00
 Total Fare: 0.00</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>10
 0
@@ -4791,14 +6597,14 @@
 5</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Distance Fare: 10.00
 Waiting Fare: 0.00
 Total Fare: 10.00</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0
 1
@@ -4806,14 +6612,14 @@
 1</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Distance Fare: 12.00
 Waiting Fare: 1.00
 Total Fare: 13.00</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>100
 50
@@ -4821,15 +6627,14 @@
 0.5</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Distance Fare: 700.00
 Waiting Fare: 60.00
 Total Fare: 760.00</t>
         </is>
       </c>
-      <c r="AF26" s="3" t="n"/>
-      <c r="AG26" s="3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>base_fare = float(input())
 distance_km = float(input())
@@ -4843,15 +6648,14 @@
 print(f"Total Fare: {total_fare:.2f}")</t>
         </is>
       </c>
-      <c r="AH26" s="2" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Grocery Store Multi-Item Bill</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>A grocery billing counter needs the subtotal across two items, the tax on that subtotal, and the final payable amount. Write a program that reads the price and quantity of two items and a tax percentage, then prints the subtotal, the tax amount, and the total, each rounded to two decimal places.
 ### Input Format
@@ -4862,67 +6666,75 @@
 - Line 5: Tax percentage
 ### Output Format
 ```
-Subtotal: &lt;subtotal&gt;
-Tax: &lt;tax&gt;
-Total: &lt;total&gt;
+Subtotal: 90.00
+Tax: 4.50
+Total: 94.50
 ```
+### Example Walkthrough
+In the sample, item 1 costs `20` for a quantity of `3`, and item 2 costs `15` for a quantity of `2`, with a `5` percent tax. The subtotal is `20.0 x 3 + 15.0 x 2 = 90.0`, the tax is `90.0 x 5 / 100 = 4.5`, and the total is `94.5`. Rounded to two decimal places, the program prints `Subtotal: 90.00`, `Tax: 4.50`, and `Total: 94.50`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" s="2" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" s="2" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q27" s="2" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R27" s="3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>40
 3
@@ -4931,14 +6743,14 @@
 5</t>
         </is>
       </c>
-      <c r="S27" s="3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Subtotal: 170.00
 Tax: 8.50
 Total: 178.50</t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>99.5
 1
@@ -4947,14 +6759,14 @@
 12</t>
         </is>
       </c>
-      <c r="U27" s="3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Subtotal: 159.50
 Tax: 19.14
 Total: 178.64</t>
         </is>
       </c>
-      <c r="V27" s="3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>10
 10
@@ -4963,14 +6775,14 @@
 0</t>
         </is>
       </c>
-      <c r="W27" s="3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Subtotal: 125.00
 Tax: 0.00
 Total: 125.00</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0
 0
@@ -4979,14 +6791,14 @@
 0</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Subtotal: 0.00
 Tax: 0.00
 Total: 0.00</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>10
 1
@@ -4995,14 +6807,14 @@
 5</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Subtotal: 10.00
 Tax: 0.50
 Total: 10.50</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>1
 1
@@ -5011,14 +6823,14 @@
 100</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Subtotal: 2.00
 Tax: 2.00
 Total: 4.00</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>50
 2
@@ -5027,15 +6839,14 @@
 0</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Subtotal: 200.00
 Tax: 0.00
 Total: 200.00</t>
         </is>
       </c>
-      <c r="AF27" s="3" t="n"/>
-      <c r="AG27" s="3" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>price1 = float(input())
 qty1 = int(input())
@@ -5050,15 +6861,14 @@
 print(f"Total: {total:.2f}")</t>
         </is>
       </c>
-      <c r="AH27" s="2" t="n"/>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Exam Result Aggregator with Logical Check</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>A result-processing tool reports a student's total marks, average, and whether they cleared the passing mark in every one of three subjects, without yet using a conditional statement. Write a program that reads three subject marks and a passing mark, then prints the total, the average, and whether all three subjects individually met or exceeded the passing mark.
 ### Input Format
@@ -5068,67 +6878,75 @@
 - Line 4: Passing marks
 ### Output Format
 ```
-Total: &lt;total&gt;
-Average: &lt;average&gt;
-All Passed: &lt;True/False&gt;
+Total: 255.0
+Average: 85.0
+All Passed: True
 ```
+### Example Walkthrough
+In the sample, the three marks are `80`, `85`, and `90`, against a passing mark of `40`. The total is `255.0` and the average is `85.0`. Since every mark is at least `40`, `All Passed` evaluates to `True`, so the program prints `Total: 255.0`, `Average: 85.0`, and `All Passed: True`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>arithmetic-operators</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>comparison-and-logical-operators</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" s="2" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" s="2" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q28" s="2" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R28" s="3" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>80
 75
@@ -5136,14 +6954,14 @@
 40</t>
         </is>
       </c>
-      <c r="S28" s="3" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Total: 245.0
 Average: 81.66666666666667
 All Passed: True</t>
         </is>
       </c>
-      <c r="T28" s="3" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>30
 75
@@ -5151,14 +6969,14 @@
 40</t>
         </is>
       </c>
-      <c r="U28" s="3" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Total: 195.0
 Average: 65.0
 All Passed: False</t>
         </is>
       </c>
-      <c r="V28" s="3" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>40
 40
@@ -5166,14 +6984,14 @@
 40</t>
         </is>
       </c>
-      <c r="W28" s="3" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Total: 120.0
 Average: 40.0
 All Passed: True</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0
 0
@@ -5181,14 +6999,14 @@
 0</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Total: 0.0
 Average: 0.0
 All Passed: True</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>40
 39.99
@@ -5196,14 +7014,14 @@
 40</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Total: 119.99000000000001
 Average: 39.99666666666667
 All Passed: False</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>100
 100
@@ -5211,14 +7029,14 @@
 0</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Total: 300.0
 Average: 100.0
 All Passed: True</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>50
 50
@@ -5226,15 +7044,14 @@
 40</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Total: 139.99
 Average: 46.663333333333334
 All Passed: False</t>
         </is>
       </c>
-      <c r="AF28" s="3" t="n"/>
-      <c r="AG28" s="3" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>marks1 = float(input())
 marks2 = float(input())
@@ -5248,15 +7065,14 @@
 print("All Passed:", all_passed)</t>
         </is>
       </c>
-      <c r="AH28" s="2" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Currency and Tax Combined Converter</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>An import invoicing tool converts a foreign payment to Rupees and then applies an import tax on the converted amount. Write a program that reads an amount in US Dollars, the exchange rate, and the tax percentage, then prints the converted amount, the tax amount, and the final payable amount, each rounded to two decimal places.
 ### Input Format
@@ -5265,166 +7081,173 @@
 - Line 3: Tax percentage
 ### Output Format
 ```
-Converted: &lt;converted&gt;
-Tax: &lt;tax&gt;
-Final Amount: &lt;final_amount&gt;
+Converted: 8300.00
+Tax: 415.00
+Final Amount: 8715.00
 ```
+### Example Walkthrough
+In the sample, the amount is `100` dollars at a rate of `83` and a tax of `5` percent. The converted amount is `100.0 x 83.0 = 8300.0`, the tax is `8300.0 x 5 / 100 = 415.0`, and the final amount is `8715.0`. Rounded to two decimal places, the program prints `Converted: 8300.00`, `Tax: 415.00`, and `Final Amount: 8715.00`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" s="2" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" s="2" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q29" s="2" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R29" s="3" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>100
 83
 18</t>
         </is>
       </c>
-      <c r="S29" s="3" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Converted: 8300.00
 Tax: 1494.00
 Final Amount: 9794.00</t>
         </is>
       </c>
-      <c r="T29" s="3" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>250
 82.5
 5</t>
         </is>
       </c>
-      <c r="U29" s="3" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Converted: 20625.00
 Tax: 1031.25
 Final Amount: 21656.25</t>
         </is>
       </c>
-      <c r="V29" s="3" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>40
 83.25
 12</t>
         </is>
       </c>
-      <c r="W29" s="3" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Converted: 3330.00
 Tax: 399.60
 Final Amount: 3729.60</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0
 83
 18</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Converted: 0.00
 Tax: 0.00
 Final Amount: 0.00</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>100
 0
 18</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Converted: 0.00
 Tax: 0.00
 Final Amount: 0.00</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>100
 83
 0</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Converted: 8300.00
 Tax: 0.00
 Final Amount: 8300.00</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1
 1
 1</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Converted: 1.00
 Tax: 0.01
 Final Amount: 1.01</t>
         </is>
       </c>
-      <c r="AF29" s="3" t="n"/>
-      <c r="AG29" s="3" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>usd_amount = float(input())
 exchange_rate = float(input())
@@ -5437,15 +7260,14 @@
 print(f"Final Amount: {final_amount:.2f}")</t>
         </is>
       </c>
-      <c r="AH29" s="2" t="n"/>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Password Strength Score</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>A signup form gives a numeric strength score to a new password and flags whether it counts as strong, without yet using a conditional statement. Write a program that reads the password length, whether it contains a digit (1 for yes, 0 for no), and whether it contains an uppercase letter (1 for yes, 0 for no), then prints the strength score and whether the password is strong. The score is the length plus 5 points for containing a digit and 5 points for containing an uppercase letter. A password is strong only if its length is at least 8, it contains a digit, and it contains an uppercase letter.
 ### Input Format
@@ -5454,158 +7276,165 @@
 - Line 3: Contains an uppercase letter (1 or 0)
 ### Output Format
 ```
-Score: &lt;score&gt;
-Strong: &lt;True/False&gt;
+Score: 20
+Strong: True
 ```
+### Example Walkthrough
+In the sample, the length is `10`, and both `has_digit` and `has_upper` are `1`. The score is `10 + 5 + 5 = 20`, and since the length is at least `8` and both flags are `1`, the password is `Strong: True`. The program prints `Score: 20` and `Strong: True`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>arithmetic-operators</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>comparison-and-logical-operators</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" s="2" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" s="2" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q30" s="2" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R30" s="3" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>10
 1
 1</t>
         </is>
       </c>
-      <c r="S30" s="3" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Score: 20
 Strong: True</t>
         </is>
       </c>
-      <c r="T30" s="3" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>6
 1
 0</t>
         </is>
       </c>
-      <c r="U30" s="3" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Score: 11
 Strong: False</t>
         </is>
       </c>
-      <c r="V30" s="3" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>8
 0
 1</t>
         </is>
       </c>
-      <c r="W30" s="3" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Score: 13
 Strong: False</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0
 0
 0</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Score: 0
 Strong: False</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>7
 1
 1</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Score: 17
 Strong: False</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>8
 1
 0</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Score: 13
 Strong: False</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>20
 0
 0</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Score: 20
 Strong: False</t>
         </is>
       </c>
-      <c r="AF30" s="3" t="n"/>
-      <c r="AG30" s="3" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>length = int(input())
 has_digit = int(input())
@@ -5616,15 +7445,14 @@
 print("Strong:", is_strong)</t>
         </is>
       </c>
-      <c r="AH30" s="2" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Library Membership Renewal Fee</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>The library renewal desk gives students a discount on their renewal fee, without yet using a conditional statement to check whether the member is a student. Write a program that reads the base annual fee, the number of years being renewed, whether the member is a student (1 for yes, 0 for no), and the student discount percentage, then prints the total fee before discount, the discount amount, and the final payable fee, each rounded to two decimal places. The discount only applies when the member is a student, achieved by multiplying the discount amount by the student flag.
 ### Input Format
@@ -5634,67 +7462,75 @@
 - Line 4: Student discount percentage
 ### Output Format
 ```
-Total Before Discount: &lt;total&gt;
-Discount: &lt;discount&gt;
-Final Fee: &lt;final_fee&gt;
+Total Before Discount: 1000.00
+Discount: 100.00
+Final Fee: 900.00
 ```
+### Example Walkthrough
+In the sample, the base fee is `500` for `2` years, the member is a student (`1`), and the discount is `10` percent. The total before discount is `500.0 x 2 = 1000.0`. Since the student flag is `1`, the discount applies in full: `1000.0 x 10 / 100 x 1 = 100.0`. The final fee is `1000.0 - 100.0 = 900.0`. The program prints `Total Before Discount: 1000.00`, `Discount: 100.00`, and `Final Fee: 900.00`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>operators</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" s="2" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" s="2" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q31" s="2" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R31" s="3" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>500
 2
@@ -5702,14 +7538,14 @@
 20</t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Total Before Discount: 1000.00
 Discount: 200.00
 Final Fee: 800.00</t>
         </is>
       </c>
-      <c r="T31" s="3" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>500
 2
@@ -5717,14 +7553,14 @@
 20</t>
         </is>
       </c>
-      <c r="U31" s="3" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Total Before Discount: 1000.00
 Discount: 0.00
 Final Fee: 1000.00</t>
         </is>
       </c>
-      <c r="V31" s="3" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>750
 1
@@ -5732,14 +7568,14 @@
 15</t>
         </is>
       </c>
-      <c r="W31" s="3" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Total Before Discount: 750.00
 Discount: 112.50
 Final Fee: 637.50</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0
 1
@@ -5747,14 +7583,14 @@
 20</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Total Before Discount: 0.00
 Discount: 0.00
 Final Fee: 0.00</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>500
 0
@@ -5762,14 +7598,14 @@
 20</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Total Before Discount: 0.00
 Discount: 0.00
 Final Fee: 0.00</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>500
 2
@@ -5777,14 +7613,14 @@
 0</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Total Before Discount: 1000.00
 Discount: 0.00
 Final Fee: 1000.00</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1000
 5
@@ -5792,15 +7628,14 @@
 100</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Total Before Discount: 5000.00
 Discount: 5000.00
 Final Fee: 0.00</t>
         </is>
       </c>
-      <c r="AF31" s="3" t="n"/>
-      <c r="AG31" s="3" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>base_fee = float(input())
 years = int(input())
@@ -5814,7 +7649,513 @@
 print(f"Final Fee: {final_fee:.2f}")</t>
         </is>
       </c>
-      <c r="AH31" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Wallet Update</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Wallet Update. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Balance
+- Line 2: Deposit
+- Line 3: Expense
+### Output Format
+```
+125.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>assignment-operators</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>100
+50
+25</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0
+10
+3</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>500
+0
+100</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1000
+250
+125</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1125.0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>-10
+20
+5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>75.5
+4.5
+10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1
+1
+2</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>b=float(input())
+b+=float(input())
+b-=float(input())
+print(b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Gate Pass Boolean</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Gate Pass Boolean. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Age
+- Line 2: True/False paid
+### Output Format
+```
+True
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>comparison-and-logical-operators</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>18
+True</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>17
+True</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>20
+False</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>21
+True</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0
+False</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>100
+True</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>18
+False</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>age=int(input())
+paid=input()=="True"
+print(age&gt;=18 and paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Cast Sum Product</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Cast Sum Product. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: First
+- Line 2: Second
+### Output Format
+```
+Sum: 5
+Product: 6
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>data-types-and-operators</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>type-conversion</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2
+3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Sum: 5
+Product: 6</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>10
+5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sum: 15
+Product: 50</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0
+7</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sum: 7
+Product: 0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-2
+4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Sum: 2
+Product: -8</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>100
+100</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Sum: 200
+Product: 10000</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1
+999</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sum: 1000
+Product: 999</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>-5
+-6</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Sum: -11
+Product: 30</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>a=int(input())
+b=int(input())
+print("Sum:", a+b)
+print("Product:", a*b)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content/Question Bank/Coding Questions/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - Coding Questions.xlsx
@@ -1948,16 +1948,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for GST Bill Total. Read the input values and print the required result exactly.
+          <t>A grocery store's billing counter needs to add GST to every purchase before printing the final amount on the receipt. GST here is a flat 18 percent of the item's price.
+Write a program that reads the price of an item as a decimal number and prints the final amount after adding 18 percent GST, rounded to exactly two decimal places.
 ### Input Format
-- Line 1: Amount
+- Line 1: Price of the item
 ### Output Format
 ```
 118.0
 ```
+### Example Walkthrough
+In the sample, the price is 100. The GST is 100 x 18 / 100 = 18, so the final amount is 100 + 18 = 118.0.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2102,16 +2105,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Minutes Split. Read the input values and print the required result exactly.
+          <t>A bus tracking app receives a trip's duration in total minutes from the GPS unit, but displays it to passengers in hours and minutes so it is easier to read.
+Write a program that reads the trip duration in minutes as a whole number and prints it split into hours and remaining minutes, in the form `&lt;hours&gt; hours &lt;minutes&gt; minutes`.
 ### Input Format
-- Line 1: Minutes
+- Line 1: Duration in minutes
 ### Output Format
 ```
 2 hours 5 minutes
 ```
+### Example Walkthrough
+In the sample, the duration is 125 minutes. Dividing by 60 gives 2 whole hours (120 minutes), leaving a remainder of 5 minutes, so the program prints `2 hours 5 minutes`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3794,7 +3800,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Name Age Line. Read the input values and print the required result exactly.
+          <t>The college attendance kiosk prints a one-line summary for every student who taps their ID card, combining their name and age into a single readable sentence.
+Write a program that reads a student's name and age, then prints a line in the form `&lt;name&gt; is &lt;age&gt; years old`.
 ### Input Format
 - Line 1: Name
 - Line 2: Age
@@ -3802,9 +3809,11 @@
 ```
 Asha is 19 years old
 ```
+### Example Walkthrough
+In the sample, the name is Asha and the age is 19, so the program prints `Asha is 19 years old`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Name is a valid string with no leading or trailing spaces.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3957,18 +3966,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Remainder Counter. Read the input values and print the required result exactly.
+          <t>A warehouse worker is packing items into boxes that each hold a fixed number of items. Before sealing the shipment, the packing software needs to report how many full boxes were made and how many items are left over.
+Write a program that reads the total number of items and the box size, then prints the number of full boxes and the number of leftover items on separate lines.
 ### Input Format
-- Line 1: Items
-- Line 2: Group size
+- Line 1: Total number of items
+- Line 2: Box size
 ### Output Format
 ```
 Full groups: 3
 Left over: 2
 ```
+### Example Walkthrough
+In the sample, there are 17 items and each box holds 5. Dividing gives 17 // 5 = 3 full boxes, with 17 % 5 = 2 items left over, so the program prints `Full groups: 3` and `Left over: 2`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5564,17 +5576,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Compare Scores. Read the input values and print the required result exactly.
+          <t>A sports quiz app wants to instantly tell which of two contestants scored higher, so it can highlight the round's leader on screen.
+Write a program that reads two scores and prints `True` if the first score is strictly greater than the second, and `False` otherwise.
 ### Input Format
-- Line 1: First
-- Line 2: Second
+- Line 1: First score
+- Line 2: Second score
 ### Output Format
 ```
 True
 ```
+### Example Walkthrough
+In the sample, the first score is 90 and the second is 80. Since 90 is greater than 80, the program prints `True`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5727,17 +5742,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Discount Price. Read the input values and print the required result exactly.
+          <t>An online store applies a seasonal discount to every product at checkout, and the app needs to show the discounted price instantly once the customer enters the discount code.
+Write a program that reads the original price and the discount percentage, then prints the price after the discount is applied, rounded to exactly two decimal places.
 ### Input Format
-- Line 1: Price
-- Line 2: Discount percent
+- Line 1: Original price
+- Line 2: Discount percentage
 ### Output Format
 ```
 90.0
 ```
+### Example Walkthrough
+In the sample, the price is 100 with a 10 percent discount. The discount amount is 100 x 10 / 100 = 10, so the final price is 100 - 10 = 90.0.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5890,7 +5908,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Precedence Value. Read the input values and print the required result exactly.
+          <t>A quiz app calculates a player's final score as a base score plus a bonus, where the bonus is the number of bonus questions answered correctly multiplied by the points awarded per bonus question. The app computes this directly as `a + b * c`, relying on Python evaluating multiplication before addition.
+Write a program that reads three whole numbers `a`, `b`, and `c`, then prints the value of the expression `a + b * c`.
 ### Input Format
 - Line 1: a
 - Line 2: b
@@ -5899,9 +5918,11 @@
 ```
 14
 ```
+### Example Walkthrough
+In the sample, a is 2, b is 3, and c is 4. Because multiplication happens before addition, the expression evaluates as 2 + (3 x 4) = 2 + 12 = 14.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -7658,18 +7679,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Wallet Update. Read the input values and print the required result exactly.
+          <t>A digital wallet app processes transactions in order: it starts from the user's opening balance, adds a top-up, then subtracts a purchase. The balance is updated in place using augmented assignment at each step.
+Write a program that reads the starting balance, the top-up amount, and the purchase amount, updates the balance with `balance += top_up` followed by `balance -= purchase`, and prints the final balance.
 ### Input Format
-- Line 1: Balance
-- Line 2: Deposit
-- Line 3: Expense
+- Line 1: Starting balance
+- Line 2: Top-up amount
+- Line 3: Purchase amount
 ### Output Format
 ```
 125.0
 ```
+### Example Walkthrough
+In the sample, the balance starts at 100. Adding a top-up of 50 makes it 150, then subtracting a purchase of 25 makes it 125.0, which the program prints.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7830,17 +7854,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Gate Pass Boolean. Read the input values and print the required result exactly.
+          <t>A hostel's visitor gate pass system only issues a pass automatically when a visitor is an adult (18 years or older) AND has already paid the entry fee at the counter. The security guard's tablet reads both pieces of information and shows whether the pass should be granted.
+Write a program that reads the visitor's age and whether they have paid (`True` or `False`), then prints `True` if the visitor is 18 or older AND has paid, and `False` otherwise.
 ### Input Format
 - Line 1: Age
-- Line 2: True/False paid
+- Line 2: `True` or `False` indicating whether the visitor has paid
 ### Output Format
 ```
 True
 ```
+### Example Walkthrough
+In the sample, the age is 18 and paid is `True`. Since 18 is greater than or equal to 18 and the visitor has paid, both conditions are true, so the program prints `True`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- Age is a valid whole number in the ranges implied by the examples.
+- The paid input is always exactly `True` or `False`.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7993,18 +8021,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Cast Sum Product. Read the input values and print the required result exactly.
+          <t>A calculator widget lets a user type two numbers into text boxes, but every value read from a text box arrives as a string. Before the widget can do any arithmetic, it must convert each entry to an integer.
+Write a program that reads two whole numbers (converting each from text to an integer), then prints their sum and product on separate lines in the form `Sum: &lt;value&gt;` and `Product: &lt;value&gt;`.
 ### Input Format
-- Line 1: First
-- Line 2: Second
+- Line 1: First number
+- Line 2: Second number
 ### Output Format
 ```
 Sum: 5
 Product: 6
 ```
+### Example Walkthrough
+In the sample, the numbers are 2 and 3. Converting both to integers and computing gives a sum of 2 + 3 = 5 and a product of 2 x 3 = 6, so the program prints `Sum: 5` and `Product: 6`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 2 - Data Types and Operators/Unit 2 - Data Types and Operators - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,15 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,17 +598,11 @@
         <is>
           <t>The weather display board near the college gate shows the day's temperature, but exchange students keep asking what it means in Fahrenheit. The maintenance team decides the board should show both units side by side.
 Write a program that reads the temperature in Celsius as a decimal (`float`) number and converts it using the formula Fahrenheit = Celsius x 9/5 + 32. Print one line in the form `&lt;celsius&gt;C is &lt;fahrenheit&gt;F`, where both values are the decimal numbers your program worked with.
-### Input Format
-- Line 1: Temperature in Celsius
-### Output Format
-```
-0.0C is 32.0F
-```
 ### Example Walkthrough
 In the sample, the input is 0. Read as a decimal number it becomes 0.0, and the conversion gives 0.0 x 9/5 + 32 = 32.0. So the program prints `0.0C is 32.0F`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -753,8 +734,8 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>celsius = float(input())
-fahrenheit = celsius * 9 / 5 + 32
+          <t>celsius = float(input())           # read the Celsius temperature as a decimal number
+fahrenheit = celsius * 9 / 5 + 32  # apply the Celsius-to-Fahrenheit formula
 print(f"{celsius}C is {fahrenheit}F")</t>
         </is>
       </c>
@@ -769,17 +750,11 @@
         <is>
           <t>When Meena signed up on a shopping app, the form saved her age as plain text - just characters, not something you can do maths with. The loyalty system now wants to add 5 bonus points to that number to set her starting score, so the text must first be turned into a real number.
 Write a program that reads the age, converts it from text to a whole number (integer), adds 5, and prints the result in the form `New Value: &lt;new_value&gt;`.
-### Input Format
-- Line 1: Age (entered as text)
-### Output Format
-```
-New Value: 25
-```
 ### Example Walkthrough
 In the sample, the input is the text `20`. Converting it to an integer gives the number 20, and adding 5 gives 25. The program therefore prints `New Value: 25`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -911,9 +886,9 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>age_text = input()
-age = int(age_text)
-new_value = age + 5
+          <t>age_text = input()      # age arrives as text from the signup form
+age = int(age_text)     # convert text to a whole number so we can add to it
+new_value = age + 5     # add the bonus points
 print("New Value:", new_value)</t>
         </is>
       </c>
@@ -928,18 +903,11 @@
         <is>
           <t>Three friends reach the cinema just in time for the evening show, and the person at the counter needs the group's total in one go. The billing screen simply multiplies the ticket price by the number of tickets.
 Write a program that reads the price of one ticket (a decimal number) and the number of tickets (a whole number), multiplies them, and prints the total in the form `Total: Rs.&lt;total&gt;`.
-### Input Format
-- Line 1: Price per ticket
-- Line 2: Number of tickets
-### Output Format
-```
-Total: Rs.450.0
-```
 ### Example Walkthrough
 In the sample, the price is 150 and the count is 3. Because the price is read as a decimal number, 150 x 3 gives 450.0, and the program prints `Total: Rs.450.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1078,9 +1046,9 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>price = float(input())
-count = int(input())
-total = price * count
+          <t>price = float(input())   # price of a single ticket
+count = int(input())     # number of tickets bought
+total = price * count    # total cost for the group
 print("Total: Rs.", total, sep="")</t>
         </is>
       </c>
@@ -1095,17 +1063,11 @@
         <is>
           <t>Priya takes an auto rickshaw from the railway station to her college. The meter follows a simple rule: a fixed base fare of Rs.20 the moment you sit down, plus Rs.10 for every kilometre travelled.
 Write a program that reads the distance in kilometres and prints the total fare - the base fare of 20 plus 10 times the distance - in the form `Fare: Rs.&lt;fare&gt;`.
-### Input Format
-- Line 1: Distance in kilometres
-### Output Format
-```
-Fare: Rs.70.0
-```
 ### Example Walkthrough
 In the sample, the distance is 5 km. The distance part of the fare is 10 x 5 = 50, and adding the base fare of 20 gives 70.0 (a decimal number, since the distance is read as one). The program prints `Fare: Rs.70.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1237,8 +1199,8 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>distance = float(input())
-fare = 20 + distance * 10
+          <t>distance = float(input())    # distance travelled in km
+fare = 20 + distance * 10    # fixed base fare plus per-km charge
 print("Fare: Rs.", fare, sep="")</t>
         </is>
       </c>
@@ -1253,18 +1215,11 @@
         <is>
           <t>A campus fitness app builds a health profile for every member, and the first number it computes is the Body Mass Index (BMI). BMI is simply a person's weight divided by the square of their height - that is, the height multiplied by itself.
 Write a program that reads the weight in kilograms and the height in metres (both decimal numbers) and prints the BMI in the form `BMI: &lt;bmi&gt;`, without any rounding.
-### Input Format
-- Line 1: Weight in kilograms
-- Line 2: Height in metres
-### Output Format
-```
-BMI: 22.857142857142858
-```
 ### Example Walkthrough
 In the sample, the weight is 70 and the height is 1.75. Squaring the height gives 1.75 x 1.75 = 3.0625, and dividing 70 by 3.0625 gives 22.857142857142858. The program prints this full value: `BMI: 22.857142857142858`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1403,9 +1358,9 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>weight = float(input())
-height = float(input())
-bmi = weight / (height ** 2)
+          <t>weight = float(input())       # weight in kilograms
+height = float(input())       # height in metres
+bmi = weight / (height ** 2)  # BMI formula: weight divided by height squared
 print("BMI:", bmi)</t>
         </is>
       </c>
@@ -1420,18 +1375,11 @@
         <is>
           <t>Rahul's cousin in the US has sent him some dollars for his semester expenses, and the travel desk near campus converts them at the day's exchange rate. The clerk types in the dollar amount and the rate, and the screen shows the rupee value.
 Write a program that reads the amount in US Dollars and the exchange rate (rupees per dollar), multiplies them, and prints the result in the form `Amount in INR: &lt;inr&gt;`.
-### Input Format
-- Line 1: Amount in US Dollars
-- Line 2: Exchange rate (INR per USD)
-### Output Format
-```
-Amount in INR: 8300.0
-```
 ### Example Walkthrough
 In the sample, the amount is 100 dollars and the rate is 83 rupees per dollar. Multiplying gives 100 x 83 = 8300.0 (a decimal number, since the inputs are read as decimals). The program prints `Amount in INR: 8300.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1570,9 +1518,9 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>usd_amount = float(input())
-exchange_rate = float(input())
-inr = usd_amount * exchange_rate
+          <t>usd_amount = float(input())        # amount received in US Dollars
+exchange_rate = float(input())     # rupees per dollar today
+inr = usd_amount * exchange_rate   # convert dollars to rupees
 print("Amount in INR:", inr)</t>
         </is>
       </c>
@@ -1587,19 +1535,11 @@
         <is>
           <t>The festival sale is live on an online store, and shoppers want to see exactly how much they save before paying. For each product, the page shows the discount amount and the price after the discount.
 Write a program that reads the original price and the discount percentage. The discount amount is price x percentage / 100, and the final price is the original price minus that discount. Print the two results on two lines in the form shown below.
-### Input Format
-- Line 1: Original price
-- Line 2: Discount percentage
-### Output Format
-```
-Discount: 200.0
-Final Price: 800.0
-```
 ### Example Walkthrough
 In the sample, the price is 1000 and the discount is 20 percent. The discount amount is 1000 x 20 / 100 = 200.0, and the final price is 1000 - 200.0 = 800.0. The program prints `Discount: 200.0` on the first line and `Final Price: 800.0` on the second.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1747,8 +1687,8 @@
         <is>
           <t>price = float(input())
 discount_percent = float(input())
-discount = price * discount_percent / 100
-final_price = price - discount
+discount = price * discount_percent / 100  # amount saved
+final_price = price - discount              # price after the discount
 print("Discount:", discount)
 print("Final Price:", final_price)</t>
         </is>
@@ -1764,20 +1704,11 @@
         <is>
           <t>The monthly electricity bill for Anil's house has two parts: a fixed charge that stays the same every month, and a variable charge that depends on how many units of power were used. The provider's billing software prints both the variable charge and the grand total.
 Write a program that reads the units consumed, the rate per unit, and the fixed monthly charge. Compute the variable charge as units x rate, add the fixed charge to get the total bill, and print both values rounded to exactly two decimal places.
-### Input Format
-- Line 1: Units consumed
-- Line 2: Rate per unit
-- Line 3: Fixed monthly charge
-### Output Format
-```
-Variable Charge: 975.00
-Total Bill: 1075.00
-```
 ### Example Walkthrough
 In the sample, 150 units at 6.5 per unit give a variable charge of 150 x 6.5 = 975, and adding the fixed charge of 100 gives a total of 1075. Shown with two decimal places, the program prints `Variable Charge: 975.00` and `Total Bill: 1075.00`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1930,11 +1861,11 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>units = float(input())
-rate_per_unit = float(input())
-fixed_charge = float(input())
-variable_charge = units * rate_per_unit
-total_bill = fixed_charge + variable_charge
+          <t>units = float(input())            # units of electricity consumed
+rate_per_unit = float(input())    # cost per unit
+fixed_charge = float(input())     # fixed monthly charge
+variable_charge = units * rate_per_unit       # charge based on usage
+total_bill = fixed_charge + variable_charge   # fixed charge plus variable charge
 print(f"Variable Charge: {variable_charge:.2f}")
 print(f"Total Bill: {total_bill:.2f}")</t>
         </is>
@@ -1950,17 +1881,11 @@
         <is>
           <t>A grocery store's billing counter needs to add GST to every purchase before printing the final amount on the receipt. GST here is a flat 18 percent of the item's price.
 Write a program that reads the price of an item as a decimal number and prints the final amount after adding 18 percent GST, rounded to exactly two decimal places.
-### Input Format
-- Line 1: Price of the item
-### Output Format
-```
-118.0
-```
 ### Example Walkthrough
 In the sample, the price is 100. The GST is 100 x 18 / 100 = 18, so the final amount is 100 + 18 = 118.0.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2092,8 +2017,8 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>a=float(input())
-print(round(a*1.18,2))</t>
+          <t>a=float(input())     # price of the item
+print(round(a*1.18,2))  # add 18% GST in one step, rounded to 2 decimal places</t>
         </is>
       </c>
     </row>
@@ -2107,17 +2032,11 @@
         <is>
           <t>A bus tracking app receives a trip's duration in total minutes from the GPS unit, but displays it to passengers in hours and minutes so it is easier to read.
 Write a program that reads the trip duration in minutes as a whole number and prints it split into hours and remaining minutes, in the form `&lt;hours&gt; hours &lt;minutes&gt; minutes`.
-### Input Format
-- Line 1: Duration in minutes
-### Output Format
-```
-2 hours 5 minutes
-```
 ### Example Walkthrough
 In the sample, the duration is 125 minutes. Dividing by 60 gives 2 whole hours (120 minutes), leaving a remainder of 5 minutes, so the program prints `2 hours 5 minutes`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2249,4110 +2168,3388 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>m=int(input())
-print(m//60, "hours", m%60, "minutes")</t>
+          <t>m=int(input())  # total trip duration in minutes
+print(m//60, "hours", m%60, "minutes")  # // gives whole hours, % gives the leftover minutes</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Restaurant Tip Splitter</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Four friends celebrate the end of exams at a restaurant, and when the bill arrives they want to split it fairly - including the tip. One of them opens a bill-splitting app that works out the tip, the new total, and each person's share.
 Write a program that reads the bill amount, the tip percentage, and the number of people. The tip is bill x percentage / 100, the total is the bill plus the tip, and the per-person share is the total divided by the number of people. Print all three values, each rounded to exactly two decimal places.
-### Input Format
-- Line 1: Bill amount
-- Line 2: Tip percentage
-- Line 3: Number of people
-### Output Format
-```
-Tip: 120.00
-Total: 1320.00
-Per Person: 330.00
-```
 ### Example Walkthrough
 In the sample, the bill is 1200 with a 10 percent tip, split among 4 people. The tip is 1200 x 10 / 100 = 120, the total is 1200 + 120 = 1320, and each person pays 1320 / 4 = 330. With two decimal places, the program prints `Tip: 120.00`, `Total: 1320.00`, and `Per Person: 330.00`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>1200
 10
 4</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>Tip: 120.00
 Total: 1320.00
 Per Person: 330.00</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>850.5
 15
 3</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Tip: 127.58
 Total: 978.08
 Per Person: 326.03</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>500
 0
 5</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Tip: 0.00
 Total: 500.00
 Per Person: 100.00</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>0
 10
 1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Tip: 0.00
 Total: 0.00
 Per Person: 0.00</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>100
 0
 1</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Tip: 0.00
 Total: 100.00
 Per Person: 100.00</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>100
 10
 1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>Tip: 10.00
 Total: 110.00
 Per Person: 110.00</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>999.99
 33.33
 7</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>Tip: 333.30
 Total: 1333.29
 Per Person: 190.47</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>bill_amount = float(input())
 tip_percent = float(input())
 num_people = int(input())
-tip = bill_amount * tip_percent / 100
-total = bill_amount + tip
-per_person = total / num_people
+tip = bill_amount * tip_percent / 100   # tip amount from the percentage
+total = bill_amount + tip               # bill including the tip
+per_person = total / num_people         # split the total evenly
 print(f"Tip: {tip:.2f}")
 print(f"Total: {total:.2f}")
 print(f"Per Person: {per_person:.2f}")</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - Type Conversion Chain</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>A billing system receives a product's price as text from an online form - for example `199.99` - but the invoice needs a quick summary label showing just the whole-rupee part, with the paise chopped off. Getting there takes a chain of conversions: text to decimal number, then decimal number to whole number.
 Write a program that reads the price as text, converts it to a `float`, then converts that `float` to an integer (which simply drops everything after the decimal point - no rounding). Print the float value and then the integer value on two labelled lines as shown below.
-### Input Format
-- Line 1: Price (entered as text, may contain decimals)
-### Output Format
-```
-As Float: 199.99
-As Whole Rupees: 199
-```
 ### Example Walkthrough
 In the sample, the input text is `199.99`. Converting it to a `float` gives 199.99, and converting that `float` to an integer drops the .99, leaving 199. The program prints `As Float: 199.99` and then `As Whole Rupees: 199`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>type-conversion</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>199.99</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>As Float: 199.99
 As Whole Rupees: 199</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>50.5</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>As Float: 50.5
 As Whole Rupees: 50</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>As Float: 1000.0
 As Whole Rupees: 1000</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>As Float: 0.0
 As Whole Rupees: 0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>0.001</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>As Float: 0.001
 As Whole Rupees: 0</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>-5.5</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>As Float: -5.5
 As Whole Rupees: -5</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>123456.789</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>As Float: 123456.789
 As Whole Rupees: 123456</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>price_text = input()
-price_float = float(price_text)
-price_int = int(price_float)
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>price_text = input()              # price arrives as text from the online form
+price_float = float(price_text)   # convert text to a decimal number
+price_int = int(price_float)      # convert decimal to integer, dropping the paise (no rounding)
 print("As Float:", price_float)
 print("As Whole Rupees:", price_int)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Python - Canteen Cookie Boxing</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>The canteen packs cookies into boxes for the evening snack counter. Write a program that reads the total number of cookies and the number of cookies per box, then prints how many full boxes can be packed and how many cookies are left over.
-### Input Format
-- Line 1: Total cookies
-- Line 2: Cookies per box
-### Output Format
-```
-Boxes: 8
-Leftover: 2
-```
 ### Example Walkthrough
 In the sample, the total is `50` cookies with `6` per box. Dividing gives `50 // 6 = 8` full boxes, with `50 % 6 = 2` cookies left over. The program prints `Boxes: 8` and `Leftover: 2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>50
 6</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>Boxes: 8
 Leftover: 2</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>100
 9</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Boxes: 11
 Leftover: 1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>23
 5</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Boxes: 4
 Leftover: 3</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>0
 6</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Boxes: 0
 Leftover: 0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>6
 6</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>Boxes: 1
 Leftover: 0</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>1
 3</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>Boxes: 0
 Leftover: 1</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>1000000
 7</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>Boxes: 142857
 Leftover: 1</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>cookies = int(input())
-per_box = int(input())
-boxes = cookies // per_box
-leftover = cookies % per_box
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>cookies = int(input())    # total cookies to pack
+per_box = int(input())    # cookies that fit in one box
+boxes = cookies // per_box     # number of full boxes (integer division)
+leftover = cookies % per_box   # cookies remaining after the full boxes
 print("Boxes:", boxes)
 print("Leftover:", leftover)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Python - Rectangular Garden Area</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>A gardener wants to know the area of a rectangular plot before ordering grass turf. Write a program that reads the length and width of the plot in metres and prints its area.
-### Input Format
-- Line 1: Length in metres
-- Line 2: Width in metres
-### Output Format
-```
-Area: 96.0 sq.m
-```
 ### Example Walkthrough
 In the sample, the length is `12` and the width is `8`, both read as decimal numbers. Multiplying gives `12.0 x 8.0 = 96.0`, so the program prints `Area: 96.0 sq.m`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>10
 5</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>Area: 50.0 sq.m</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>12.5
 4</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Area: 50.0 sq.m</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>7
 7</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Area: 49.0 sq.m</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Area: 0.0 sq.m</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>Area: 1.0 sq.m</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>0.5
 0.5</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>Area: 0.25 sq.m</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>1000
 1000</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>Area: 1000000.0 sq.m</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>length = float(input())
 width = float(input())
-area = length * width
+area = length * width   # area of a rectangle is length times width
 print("Area:", area, "sq.m")</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Python - Full Name Tag</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>An event registration desk prints a name tag for every attendee. Write a program that reads a first name and a last name, then prints the full name joined with a space.
-### Input Format
-- Line 1: First name
-- Line 2: Last name
-### Output Format
-```
-Name Tag: Devika Rao
-```
 ### Example Walkthrough
 In the sample, the inputs are `Devika` and `Rao`. Joining them with a space gives `Devika Rao`, so the program prints `Name Tag: Devika Rao`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>strings-and-booleans</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>Asha
 Verma</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>Name Tag: Asha Verma</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Kabir
 Khan</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Name Tag: Kabir Khan</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Meera
 Iyer</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Name Tag: Meera Iyer</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>A
 B</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Name Tag: A B</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Jean-Luc
 O'Brien</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>Name Tag: Jean-Luc O'Brien</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>X
 Y</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>Name Tag: X Y</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>Ravi
 Kumar</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>Name Tag: Ravi Kumar</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>first = input()
 last = input()
-full_name = first + " " + last
+full_name = first + " " + last  # string concatenation joins the names with a space
 print("Name Tag:", full_name)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - Average of Two Tests</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>A teacher wants the average score across two unit tests for quick reporting. Write a program that reads two test scores and prints their average.
-### Input Format
-- Line 1: Score in test 1
-- Line 2: Score in test 2
-### Output Format
-```
-Average: 86.0
-```
 ### Example Walkthrough
 In the sample, the two scores are `82` and `90`. Their average is `(82.0 + 90.0) / 2 = 86.0`, so the program prints `Average: 86.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>80
 90</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>Average: 85.0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>45
 55</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Average: 50.0</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>72
 68</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Average: 70.0</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Average: 0.0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>100
 100</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>Average: 100.0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>-10
 10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>Average: 0.0</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>-20
 -30</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>Average: -25.0</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>score1 = float(input())
 score2 = float(input())
-average = (score1 + score2) / 2
+average = (score1 + score2) / 2   # average of the two scores
 print("Average:", average)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Python - Gym Membership Days</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>A gym wants to convert a membership duration given in weeks into the equivalent number of days for its records. Write a program that reads the number of weeks and prints the total number of days.
-### Input Format
-- Line 1: Number of weeks
-### Output Format
-```
-Total Days: 42
-```
 ### Example Walkthrough
 In the sample, the duration is `6` weeks. Multiplying by 7 gives `6 x 7 = 42` days, so the program prints `Total Days: 42`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>Total Days: 28</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Total Days: 84</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Total Days: 7</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Total Days: 0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Total Days: -7</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>Total Days: 364</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>Total Days: 7000</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>weeks = int(input())
-days = weeks * 7
+days = weeks * 7   # 7 days in a week
 print("Total Days:", days)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Python - Pass Mark Check</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>An online quiz platform wants to display whether a student's score meets the passing mark of 40, without yet branching the program's behaviour. Write a program that reads a score and prints whether it is greater than or equal to 40.
-### Input Format
-- Line 1: Score
-### Output Format
-```
-Pass Status: True
-```
 ### Example Walkthrough
 In the sample, the score is `55`. Since `55 &gt;= 40` is `True`, the program prints `Pass Status: True`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>comparison-and-logical-operators</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>Pass Status: True</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Pass Status: False</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Pass Status: True</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Pass Status: False</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>39.99</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>Pass Status: False</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>40.01</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Pass Status: True</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>Pass Status: False</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>score = float(input())
-is_pass = score &gt;= 40
+is_pass = score &gt;= 40   # comparison operator produces a boolean result
 print("Pass Status:", is_pass)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Name Age Line</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>The college attendance kiosk prints a one-line summary for every student who taps their ID card, combining their name and age into a single readable sentence.
 Write a program that reads a student's name and age, then prints a line in the form `&lt;name&gt; is &lt;age&gt; years old`.
-### Input Format
-- Line 1: Name
-- Line 2: Age
-### Output Format
-```
-Asha is 19 years old
-```
 ### Example Walkthrough
 In the sample, the name is Asha and the age is 19, so the program prints `Asha is 19 years old`.
 ### Constraints
 - Name is a valid string with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>input-and-output</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>Asha
 19</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>Asha is 19 years old</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Rohan
 20</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Rohan is 20 years old</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Meena
 18</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Meena is 18 years old</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Kabir
 21</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Kabir is 21 years old</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>Zoya
 17</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>Zoya is 17 years old</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>Dev
 22</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>Dev is 22 years old</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>S
 1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>S is 1 years old</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>name=input()
 age=int(input())
-print(f"{name} is {age} years old")</t>
+print(f"{name} is {age} years old")  # f-string embeds the variables directly in the text</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - Remainder Counter</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A warehouse worker is packing items into boxes that each hold a fixed number of items. Before sealing the shipment, the packing software needs to report how many full boxes were made and how many items are left over.
 Write a program that reads the total number of items and the box size, then prints the number of full boxes and the number of leftover items on separate lines.
-### Input Format
-- Line 1: Total number of items
-- Line 2: Box size
-### Output Format
-```
-Full groups: 3
-Left over: 2
-```
 ### Example Walkthrough
 In the sample, there are 17 items and each box holds 5. Dividing gives 17 // 5 = 3 full boxes, with 17 % 5 = 2 items left over, so the program prints `Full groups: 3` and `Left over: 2`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>17
 5</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>Full groups: 3
 Left over: 2</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>10
 2</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Full groups: 5
 Left over: 0</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>9
 4</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Full groups: 2
 Left over: 1</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>0
 3</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Full groups: 0
 Left over: 0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>100
 10</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Full groups: 10
 Left over: 0</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>99
 8</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>Full groups: 12
 Left over: 3</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>7
 9</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>Full groups: 0
 Left over: 7</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>items=int(input())
 size=int(input())
-print("Full groups:", items//size)
-print("Left over:", items%size)</t>
+print("Full groups:", items//size)  # // gives the number of full groups
+print("Left over:", items%size)     # % gives what remains after grouping</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Python - Canteen Bill Calculator</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>The canteen counter needs to print a short bill that includes tax. Write a program that reads an item's price, the quantity ordered, and the tax percentage, then prints the subtotal, the tax amount, and the final total.
-### Input Format
-- Line 1: Item price
-- Line 2: Quantity
-- Line 3: Tax percentage
-### Output Format
-```
-Subtotal: 150.0
-Tax: 7.5
-Total: 157.5
-```
 ### Example Walkthrough
 In the sample, the price is `50`, the quantity is `3`, and the tax is `5` percent. The subtotal is `50.0 x 3 = 150.0`, the tax is `150.0 x 5 / 100 = 7.5`, and the total is `150.0 + 7.5 = 157.5`. The program prints `Subtotal: 150.0`, `Tax: 7.5`, and `Total: 157.5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>50
 2
 5</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>Subtotal: 100.0
 Tax: 5.0
 Total: 105.0</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>120
 1
 10</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>Subtotal: 120.0
 Tax: 12.0
 Total: 132.0</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>75.5
 3
 8</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Subtotal: 226.5
 Tax: 18.12
 Total: 244.62</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>0
 1
 0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Subtotal: 0.0
 Tax: 0.0
 Total: 0.0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>10
 0
 5</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>Subtotal: 0.0
 Tax: 0.0
 Total: 0.0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>50
 2
 0</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>Subtotal: 100.0
 Tax: 0.0
 Total: 100.0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>33.33
 3
 100</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>Subtotal: 99.99
 Tax: 99.99
 Total: 199.98</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>price = float(input())
 quantity = int(input())
 tax_percent = float(input())
-subtotal = price * quantity
-tax = subtotal * tax_percent / 100
-total = subtotal + tax
+subtotal = price * quantity          # cost before tax
+tax = subtotal * tax_percent / 100   # tax on the subtotal
+total = subtotal + tax               # final payable amount
 print("Subtotal:", subtotal)
 print("Tax:", tax)
 print("Total:", total)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Python - Petrol Cost Splitter</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Four friends share a car for a road trip and want to split the petrol cost evenly, keeping track of any amount that cannot be split evenly. Write a program that reads the total petrol cost and the number of friends, then prints each friend's even share and the leftover amount.
-### Input Format
-- Line 1: Total petrol cost
-- Line 2: Number of friends
-### Output Format
-```
-Share per person: 333
-Leftover: 1
-```
 ### Example Walkthrough
 In the sample, the total cost is `1000` split among `3` friends. Each friend's even share is `1000 // 3 = 333`, with `1000 % 3 = 1` left over. The program prints `Share per person: 333` and `Leftover: 1`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>100
 3</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Share per person: 33
 Leftover: 1</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>250
 4</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Share per person: 62
 Leftover: 2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>999
 7</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Share per person: 142
 Leftover: 5</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Share per person: 0
 Leftover: 0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>Share per person: 1
 Leftover: 0</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>100
 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>Share per person: 100
 Leftover: 0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>1000000
 13</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>Share per person: 76923
 Leftover: 1</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>total_cost = int(input())
 friends = int(input())
-share = total_cost // friends
-leftover = total_cost % friends
+share = total_cost // friends    # even share per person (integer division)
+leftover = total_cost % friends  # amount that cannot be split evenly
 print("Share per person:", share)
 print("Leftover:", leftover)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - Exam Score Aggregator</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>A report card generator needs the total and average of three subject marks for a student. Write a program that reads three marks and prints their total and their average.
-### Input Format
-- Line 1: Marks in subject 1
-- Line 2: Marks in subject 2
-- Line 3: Marks in subject 3
-### Output Format
-```
-Total: 255.0
-Average: 85.0
-```
 ### Example Walkthrough
 In the sample, the three marks are `80`, `85`, and `90`. Their total is `255.0` and their average is `255.0 / 3 = 85.0`, so the program prints `Total: 255.0` and `Average: 85.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>80
 75
 90</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>Total: 245.0
 Average: 81.66666666666667</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>60
 65
 70</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>Total: 195.0
 Average: 65.0</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>100
 95
 98</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Total: 293.0
 Average: 97.66666666666667</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>0
 0
 0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Total: 0.0
 Average: 0.0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>100
 100
 100</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>Total: 300.0
 Average: 100.0</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>-10
 50
 60</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>Total: 100.0
 Average: 33.333333333333336</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>33
 33
 34</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>Total: 100.0
 Average: 33.333333333333336</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>marks1 = float(input())
 marks2 = float(input())
 marks3 = float(input())
-total = marks1 + marks2 + marks3
-average = total / 3
+total = marks1 + marks2 + marks3   # sum of all three marks
+average = total / 3                # average across three subjects
 print("Total:", total)
 print("Average:", average)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - Library Fine Calculator</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>The library charges a fixed late fee plus an extra amount for every day a book is overdue. Write a program that reads the number of days a book is late and the per-day fine rate, then prints the total fine, given a fixed late fee of 10.
-### Input Format
-- Line 1: Days late
-- Line 2: Fine per day
-### Output Format
-```
-Total Fine: 16.0
-```
 ### Example Walkthrough
 In the sample, the book is `3` days late at a rate of `2` per day. The total fine is the fixed `10` plus `3 x 2.0 = 6.0`, giving `16.0`, so the program prints `Total Fine: 16.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>5
 2</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>Total Fine: 20.0</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>0
 2</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Total Fine: 10.0</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>10
 1.5</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Total Fine: 25.0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Total Fine: 10.0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>1
 0</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Total Fine: 10.0</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>100
 0.5</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>Total Fine: 60.0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>365
 5</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>Total Fine: 1835.0</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>days_late = int(input())
 fine_per_day = float(input())
-total_fine = 10 + days_late * fine_per_day
+total_fine = 10 + days_late * fine_per_day   # fixed late fee plus per-day fine
 print("Total Fine:", total_fine)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Class Average and Pass Margin</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>A teacher wants to know not just whether a student passed, but by how much they cleared (or missed) the passing mark. Write a program that reads a student's marks and the passing mark, then prints the margin by which the marks exceed the passing mark, and whether the student passed.
-### Input Format
-- Line 1: Marks obtained
-- Line 2: Passing marks
-### Output Format
-```
-Margin: 5.0
-Passed: True
-```
 ### Example Walkthrough
 In the sample, the marks are `45` against a passing mark of `40`. The margin is `45.0 - 40.0 = 5.0`, and since `45.0 &gt;= 40.0` is `True`, the program prints `Margin: 5.0` and `Passed: True`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>comparison-and-logical-operators</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>55
 40</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>Margin: 15.0
 Passed: True</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>35
 40</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Margin: -5.0
 Passed: False</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>40
 40</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Margin: 0.0
 Passed: True</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Margin: 0.0
 Passed: True</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>-10
 0</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>Margin: -10.0
 Passed: False</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>39.99
 40</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>Margin: -0.00999999999999801
 Passed: False</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>1000
 40</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>Margin: 960.0
 Passed: True</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>marks = float(input())
 passing_marks = float(input())
-margin = marks - passing_marks
-is_pass = marks &gt;= passing_marks
+margin = marks - passing_marks     # how much marks exceed (or fall short of) the pass mark
+is_pass = marks &gt;= passing_marks   # boolean check using a comparison operator
 print("Margin:", margin)
 print("Passed:", is_pass)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Python - Taxi Fare with Surge</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>A ride-hailing app applies a surge multiplier to the normal fare during peak hours. Write a program that reads the base fare, the distance travelled in kilometres, and the surge multiplier, then prints the final fare, using a rate of 12 per kilometre before the surge is applied.
-### Input Format
-- Line 1: Base fare
-- Line 2: Distance in kilometres
-- Line 3: Surge multiplier
-### Output Format
-```
-Final Fare: 255.0
-```
 ### Example Walkthrough
 In the sample, the base fare is `50`, the distance is `10` km, and the surge multiplier is `1.5`. Before the surge, the fare is `50.0 + 10.0 x 12 = 170.0`; applying the surge gives `170.0 x 1.5 = 255.0`, so the program prints `Final Fare: 255.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>30
 5
 1.5</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>Final Fare: 135.0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>20
 10
 1</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>Final Fare: 140.0</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>25
 8
 2</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Final Fare: 242.0</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>0
 0
 1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Final Fare: 0.0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>10
 0
 1</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>Final Fare: 10.0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>0
 5
 0</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>Final Fare: 0.0</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>50
 100
 0.5</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>Final Fare: 625.0</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>base_fare = float(input())
 distance_km = float(input())
 surge_multiplier = float(input())
-final_fare = (base_fare + distance_km * 12) * surge_multiplier
+final_fare = (base_fare + distance_km * 12) * surge_multiplier  # parentheses: fare first, then surge
 print("Final Fare:", final_fare)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - Augmented Score Tracker</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>A quiz app starts a player at a base score and then adds bonus points from two separate rounds. Write a program that reads a starting score and two bonus amounts, adds each bonus to the score one at a time using the += operator, and prints the final score.
-### Input Format
-- Line 1: Starting score
-- Line 2: Bonus from round 1
-- Line 3: Bonus from round 2
-### Output Format
-```
-Final Score: 135
-```
 ### Example Walkthrough
 In the sample, the starting score is `100`, with bonuses of `20` and `15`. Adding each bonus in turn with `+=` gives `100 + 20 = 120`, then `120 + 15 = 135`, so the program prints `Final Score: 135`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>assignment-operators</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>10
 5
 8</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>Final Score: 23</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>0
 20
 30</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Final Score: 50</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>100
 -10
 5</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Final Score: 95</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>0
 0
 0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Final Score: 0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>-10
 -5
 -8</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>Final Score: -23</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>0
 -100
 50</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>Final Score: -50</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>1000
 1000
 1000</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>Final Score: 3000</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>score = int(input())
 bonus1 = int(input())
 bonus2 = int(input())
-score += bonus1
-score += bonus2
+score += bonus1   # += adds bonus1 to score and stores the result back in score
+score += bonus2   # add the second bonus the same way
 print("Final Score:", score)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - Compare Scores</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A sports quiz app wants to instantly tell which of two contestants scored higher, so it can highlight the round's leader on screen.
 Write a program that reads two scores and prints `True` if the first score is strictly greater than the second, and `False` otherwise.
-### Input Format
-- Line 1: First score
-- Line 2: Second score
-### Output Format
-```
-True
-```
 ### Example Walkthrough
 In the sample, the first score is 90 and the second is 80. Since 90 is greater than 80, the program prints `True`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>comparison-and-logical-operators</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>90
 80</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>50
 50</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>10
 20</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>0
 -1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>-5
 -10</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>100
 99</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>1
 2</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>a=int(input())
 b=int(input())
-print(a&gt;b)</t>
+print(a&gt;b)  # comparison operator returns True or False</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - Discount Price</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>An online store applies a seasonal discount to every product at checkout, and the app needs to show the discounted price instantly once the customer enters the discount code.
 Write a program that reads the original price and the discount percentage, then prints the price after the discount is applied, rounded to exactly two decimal places.
-### Input Format
-- Line 1: Original price
-- Line 2: Discount percentage
-### Output Format
-```
-90.0
-```
 ### Example Walkthrough
 In the sample, the price is 100 with a 10 percent discount. The discount amount is 100 x 10 / 100 = 10, so the final price is 100 - 10 = 90.0.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>100
 10</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>250
 20</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>200.0</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>99.99
 5</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>94.99</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>500
 0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>500.0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>1000
 50</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>500.0</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>75.5
 12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>66.44</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>1
 100</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG30" t="inlineStr">
         <is>
           <t>p=float(input())
 d=float(input())
-print(round(p-p*d/100,2))</t>
+print(round(p-p*d/100,2))  # subtract the discount amount, then round to 2 decimals</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - Precedence Value</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>A quiz app calculates a player's final score as a base score plus a bonus, where the bonus is the number of bonus questions answered correctly multiplied by the points awarded per bonus question. The app computes this directly as `a + b * c`, relying on Python evaluating multiplication before addition.
 Write a program that reads three whole numbers `a`, `b`, and `c`, then prints the value of the expression `a + b * c`.
-### Input Format
-- Line 1: a
-- Line 2: b
-- Line 3: c
-### Output Format
-```
-14
-```
 ### Example Walkthrough
 In the sample, a is 2, b is 3, and c is 4. Because multiplication happens before addition, the expression evaluates as 2 + (3 x 4) = 2 + 12 = 14.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>operator-precedence</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>2
 3
 4</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>10
 5
 2</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>0
 7
 8</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>-1
 3
 5</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>6
 0
 9</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>1
 2
 3</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>100
 10
 10</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>a=int(input())
 b=int(input())
 c=int(input())
-print(a+b*c)</t>
+print(a+b*c)  # multiplication happens before addition (operator precedence)</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Hostel Mess Bill Splitter</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>The hostel mess committee collects a fixed service charge on top of the total food bill, then splits the combined amount evenly among the students, tracking any amount left over. Write a program that reads the total food bill, the number of students, and the service charge percentage, then prints the service charge, the grand total, each student's even share, and the leftover amount.
-### Input Format
-- Line 1: Total food bill
-- Line 2: Number of students
-- Line 3: Service charge percentage
-### Output Format
-```
-Service Charge: 200.0
-Grand Total: 2200.0
-Share per Student: 366
-Leftover: 4
-```
 ### Example Walkthrough
 In the sample, the food bill is `2000` split among `6` students, with a `10` percent service charge. The service charge is `2000.0 x 10 / 100 = 200.0`, giving a grand total of `2200.0`. Splitting `2200` among `6` students gives a share of `366` each, with `4` left over. The program prints `Service Charge: 200.0`, `Grand Total: 2200.0`, `Share per Student: 366`, and `Leftover: 4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>1000
 7
 5</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>Service Charge: 50.0
 Grand Total: 1050.0
@@ -6360,14 +5557,14 @@
 Leftover: 0</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>1500
 9
 10</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Service Charge: 150.0
 Grand Total: 1650.0
@@ -6375,14 +5572,14 @@
 Leftover: 3</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>799
 4
 0</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Service Charge: 0.0
 Grand Total: 799.0
@@ -6390,14 +5587,14 @@
 Leftover: 3</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>0
 1
 0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Service Charge: 0.0
 Grand Total: 0.0
@@ -6405,14 +5602,14 @@
 Leftover: 0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>100
 1
 0</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>Service Charge: 0.0
 Grand Total: 100.0
@@ -6420,14 +5617,14 @@
 Leftover: 0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>1
 1
 100</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>Service Charge: 1.0
 Grand Total: 2.0
@@ -6435,14 +5632,14 @@
 Leftover: 0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>999999
 11
 7</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>Service Charge: 69999.93
 Grand Total: 1069998.93
@@ -6450,15 +5647,15 @@
 Leftover: 6</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>total_bill = float(input())
 students = int(input())
 service_percent = float(input())
-service_charge = total_bill * service_percent / 100
-grand_total = total_bill + service_charge
-share = int(grand_total) // students
-leftover = int(grand_total) % students
+service_charge = total_bill * service_percent / 100   # charge based on percentage of the bill
+grand_total = total_bill + service_charge              # bill plus service charge
+share = int(grand_total) // students                   # even share per student (integer division)
+leftover = int(grand_total) % students                 # amount left after the even split
 print("Service Charge:", service_charge)
 print("Grand Total:", grand_total)
 print("Share per Student:", share)
@@ -6466,91 +5663,80 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Cab Trip Fare Breakdown</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>A cab aggregator's invoice shows a clear breakdown of the distance fare and the waiting-time fare before the final total, formatted to two decimal places. Write a program that reads the base fare, the distance in kilometres, the waiting time in minutes, and the per-minute waiting rate, then prints the distance fare, the waiting fare, and the total fare, each rounded to two decimal places, using a distance rate of 12 per kilometre.
-### Input Format
-- Line 1: Base fare
-- Line 2: Distance in kilometres
-- Line 3: Waiting time in minutes
-- Line 4: Rate per minute of waiting
-### Output Format
-```
-Distance Fare: 136.00
-Waiting Fare: 10.00
-Total Fare: 146.00
-```
 ### Example Walkthrough
 In the sample, the base fare is `40`, the distance is `8` km, the waiting time is `5` minutes, and the waiting rate is `2` per minute. The distance fare is `40.0 + 8.0 x 12 = 136.0`, the waiting fare is `5.0 x 2.0 = 10.0`, and the total is `146.0`. Rounded to two decimal places, the program prints `Distance Fare: 136.00`, `Waiting Fare: 10.00`, and `Total Fare: 146.00`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>20
 8
@@ -6558,14 +5744,14 @@
 2</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>Distance Fare: 116.00
 Waiting Fare: 10.00
 Total Fare: 126.00</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>15
 12.5
@@ -6573,14 +5759,14 @@
 2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>Distance Fare: 165.00
 Waiting Fare: 0.00
 Total Fare: 165.00</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>25
 6.25
@@ -6588,14 +5774,14 @@
 1.5</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>Distance Fare: 100.00
 Waiting Fare: 15.00
 Total Fare: 115.00</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>0
 0
@@ -6603,14 +5789,14 @@
 0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Distance Fare: 0.00
 Waiting Fare: 0.00
 Total Fare: 0.00</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>10
 0
@@ -6618,14 +5804,14 @@
 5</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Distance Fare: 10.00
 Waiting Fare: 0.00
 Total Fare: 10.00</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>0
 1
@@ -6633,14 +5819,14 @@
 1</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>Distance Fare: 12.00
 Waiting Fare: 1.00
 Total Fare: 13.00</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>100
 50
@@ -6648,114 +5834,102 @@
 0.5</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>Distance Fare: 700.00
 Waiting Fare: 60.00
 Total Fare: 760.00</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>base_fare = float(input())
 distance_km = float(input())
 waiting_minutes = float(input())
 rate_per_min = float(input())
-distance_fare = base_fare + distance_km * 12
-waiting_fare = waiting_minutes * rate_per_min
-total_fare = distance_fare + waiting_fare
+distance_fare = base_fare + distance_km * 12   # base fare plus per-km charge
+waiting_fare = waiting_minutes * rate_per_min  # charge for the waiting time
+total_fare = distance_fare + waiting_fare      # combined fare
 print(f"Distance Fare: {distance_fare:.2f}")
 print(f"Waiting Fare: {waiting_fare:.2f}")
 print(f"Total Fare: {total_fare:.2f}")</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Grocery Store Multi-Item Bill</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>A grocery billing counter needs the subtotal across two items, the tax on that subtotal, and the final payable amount. Write a program that reads the price and quantity of two items and a tax percentage, then prints the subtotal, the tax amount, and the total, each rounded to two decimal places.
-### Input Format
-- Line 1: Item 1 price
-- Line 2: Item 1 quantity
-- Line 3: Item 2 price
-- Line 4: Item 2 quantity
-- Line 5: Tax percentage
-### Output Format
-```
-Subtotal: 90.00
-Tax: 4.50
-Total: 94.50
-```
 ### Example Walkthrough
 In the sample, item 1 costs `20` for a quantity of `3`, and item 2 costs `15` for a quantity of `2`, with a `5` percent tax. The subtotal is `20.0 x 3 + 15.0 x 2 = 90.0`, the tax is `90.0 x 5 / 100 = 4.5`, and the total is `94.5`. Rounded to two decimal places, the program prints `Subtotal: 90.00`, `Tax: 4.50`, and `Total: 94.50`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>40
 3
@@ -6764,14 +5938,14 @@
 5</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>Subtotal: 170.00
 Tax: 8.50
 Total: 178.50</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>99.5
 1
@@ -6780,14 +5954,14 @@
 12</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>Subtotal: 159.50
 Tax: 19.14
 Total: 178.64</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>10
 10
@@ -6796,14 +5970,14 @@
 0</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Subtotal: 125.00
 Tax: 0.00
 Total: 125.00</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>0
 0
@@ -6812,14 +5986,14 @@
 0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Subtotal: 0.00
 Tax: 0.00
 Total: 0.00</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>10
 1
@@ -6828,14 +6002,14 @@
 5</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Subtotal: 10.00
 Tax: 0.50
 Total: 10.50</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>1
 1
@@ -6844,14 +6018,14 @@
 100</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>Subtotal: 2.00
 Tax: 2.00
 Total: 4.00</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>50
 2
@@ -6860,114 +6034,103 @@
 0</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>Subtotal: 200.00
 Tax: 0.00
 Total: 200.00</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>price1 = float(input())
 qty1 = int(input())
 price2 = float(input())
 qty2 = int(input())
 tax_percent = float(input())
-subtotal = price1 * qty1 + price2 * qty2
-tax = subtotal * tax_percent / 100
-total = subtotal + tax
+subtotal = price1 * qty1 + price2 * qty2   # combined cost of both items
+tax = subtotal * tax_percent / 100          # tax on the subtotal
+total = subtotal + tax                      # final payable amount
 print(f"Subtotal: {subtotal:.2f}")
 print(f"Tax: {tax:.2f}")
 print(f"Total: {total:.2f}")</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Exam Result Aggregator with Logical Check</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>A result-processing tool reports a student's total marks, average, and whether they cleared the passing mark in every one of three subjects, without yet using a conditional statement. Write a program that reads three subject marks and a passing mark, then prints the total, the average, and whether all three subjects individually met or exceeded the passing mark.
-### Input Format
-- Line 1: Marks in subject 1
-- Line 2: Marks in subject 2
-- Line 3: Marks in subject 3
-- Line 4: Passing marks
-### Output Format
-```
-Total: 255.0
-Average: 85.0
-All Passed: True
-```
 ### Example Walkthrough
 In the sample, the three marks are `80`, `85`, and `90`, against a passing mark of `40`. The total is `255.0` and the average is `85.0`. Since every mark is at least `40`, `All Passed` evaluates to `True`, so the program prints `Total: 255.0`, `Average: 85.0`, and `All Passed: True`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>comparison-and-logical-operators</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>80
 75
@@ -6975,14 +6138,14 @@
 40</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>Total: 245.0
 Average: 81.66666666666667
 All Passed: True</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>30
 75
@@ -6990,14 +6153,14 @@
 40</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>Total: 195.0
 Average: 65.0
 All Passed: False</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>40
 40
@@ -7005,14 +6168,14 @@
 40</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Total: 120.0
 Average: 40.0
 All Passed: True</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>0
 0
@@ -7020,14 +6183,14 @@
 0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Total: 0.0
 Average: 0.0
 All Passed: True</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>40
 39.99
@@ -7035,14 +6198,14 @@
 40</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>Total: 119.99000000000001
 Average: 39.99666666666667
 All Passed: False</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>100
 100
@@ -7050,14 +6213,14 @@
 0</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>Total: 300.0
 Average: 100.0
 All Passed: True</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>50
 50
@@ -7065,21 +6228,22 @@
 40</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>Total: 139.99
 Average: 46.663333333333334
 All Passed: False</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>marks1 = float(input())
 marks2 = float(input())
 marks3 = float(input())
 passing_marks = float(input())
-total = marks1 + marks2 + marks3
-average = total / 3
+total = marks1 + marks2 + marks3   # sum of all three marks
+average = total / 3                # average across three subjects
+# "and" combines three comparisons: True only if every subject meets the passing mark
 all_passed = (marks1 &gt;= passing_marks) and (marks2 &gt;= passing_marks) and (marks3 &gt;= passing_marks)
 print("Total:", total)
 print("Average:", average)
@@ -7087,471 +6251,442 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - Currency and Tax Combined Converter</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>An import invoicing tool converts a foreign payment to Rupees and then applies an import tax on the converted amount. Write a program that reads an amount in US Dollars, the exchange rate, and the tax percentage, then prints the converted amount, the tax amount, and the final payable amount, each rounded to two decimal places.
-### Input Format
-- Line 1: Amount in US Dollars
-- Line 2: Exchange rate (INR per USD)
-- Line 3: Tax percentage
-### Output Format
-```
-Converted: 8300.00
-Tax: 415.00
-Final Amount: 8715.00
-```
 ### Example Walkthrough
 In the sample, the amount is `100` dollars at a rate of `83` and a tax of `5` percent. The converted amount is `100.0 x 83.0 = 8300.0`, the tax is `8300.0 x 5 / 100 = 415.0`, and the final amount is `8715.0`. Rounded to two decimal places, the program prints `Converted: 8300.00`, `Tax: 415.00`, and `Final Amount: 8715.00`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>100
 83
 18</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>Converted: 8300.00
 Tax: 1494.00
 Final Amount: 9794.00</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>250
 82.5
 5</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>Converted: 20625.00
 Tax: 1031.25
 Final Amount: 21656.25</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>40
 83.25
 12</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>Converted: 3330.00
 Tax: 399.60
 Final Amount: 3729.60</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>0
 83
 18</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Converted: 0.00
 Tax: 0.00
 Final Amount: 0.00</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>100
 0
 18</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>Converted: 0.00
 Tax: 0.00
 Final Amount: 0.00</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>100
 83
 0</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>Converted: 8300.00
 Tax: 0.00
 Final Amount: 8300.00</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>1
 1
 1</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>Converted: 1.00
 Tax: 0.01
 Final Amount: 1.01</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>usd_amount = float(input())
 exchange_rate = float(input())
 tax_percent = float(input())
-converted = usd_amount * exchange_rate
-tax = converted * tax_percent / 100
-final_amount = converted + tax
+converted = usd_amount * exchange_rate    # convert dollars to rupees
+tax = converted * tax_percent / 100       # tax on the converted amount
+final_amount = converted + tax            # amount payable after tax
 print(f"Converted: {converted:.2f}")
 print(f"Tax: {tax:.2f}")
 print(f"Final Amount: {final_amount:.2f}")</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - Password Strength Score</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>A signup form gives a numeric strength score to a new password and flags whether it counts as strong, without yet using a conditional statement. Write a program that reads the password length, whether it contains a digit (1 for yes, 0 for no), and whether it contains an uppercase letter (1 for yes, 0 for no), then prints the strength score and whether the password is strong. The score is the length plus 5 points for containing a digit and 5 points for containing an uppercase letter. A password is strong only if its length is at least 8, it contains a digit, and it contains an uppercase letter.
-### Input Format
-- Line 1: Password length
-- Line 2: Contains a digit (1 or 0)
-- Line 3: Contains an uppercase letter (1 or 0)
-### Output Format
-```
-Score: 20
-Strong: True
-```
 ### Example Walkthrough
 In the sample, the length is `10`, and both `has_digit` and `has_upper` are `1`. The score is `10 + 5 + 5 = 20`, and since the length is at least `8` and both flags are `1`, the password is `Strong: True`. The program prints `Score: 20` and `Strong: True`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>comparison-and-logical-operators</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>10
 1
 1</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>Score: 20
 Strong: True</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>6
 1
 0</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>Score: 11
 Strong: False</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>8
 0
 1</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Score: 13
 Strong: False</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>0
 0
 0</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Score: 0
 Strong: False</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>7
 1
 1</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>Score: 17
 Strong: False</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>8
 1
 0</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>Score: 13
 Strong: False</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>20
 0
 0</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>Score: 20
 Strong: False</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>length = int(input())
-has_digit = int(input())
-has_upper = int(input())
-score = length + has_digit * 5 + has_upper * 5
+has_digit = int(input())    # 1 if the password contains a digit, else 0
+has_upper = int(input())    # 1 if the password contains an uppercase letter, else 0
+score = length + has_digit * 5 + has_upper * 5   # bonus points added only when the flag is 1
+# all three conditions must be true for the password to count as strong
 is_strong = (length &gt;= 8) and (has_digit == 1) and (has_upper == 1)
 print("Score:", score)
 print("Strong:", is_strong)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Library Membership Renewal Fee</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>The library renewal desk gives students a discount on their renewal fee, without yet using a conditional statement to check whether the member is a student. Write a program that reads the base annual fee, the number of years being renewed, whether the member is a student (1 for yes, 0 for no), and the student discount percentage, then prints the total fee before discount, the discount amount, and the final payable fee, each rounded to two decimal places. The discount only applies when the member is a student, achieved by multiplying the discount amount by the student flag.
-### Input Format
-- Line 1: Base annual fee
-- Line 2: Number of years
-- Line 3: Is student (1 or 0)
-- Line 4: Student discount percentage
-### Output Format
-```
-Total Before Discount: 1000.00
-Discount: 100.00
-Final Fee: 900.00
-```
 ### Example Walkthrough
 In the sample, the base fee is `500` for `2` years, the member is a student (`1`), and the discount is `10` percent. The total before discount is `500.0 x 2 = 1000.0`. Since the student flag is `1`, the discount applies in full: `1000.0 x 10 / 100 x 1 = 100.0`. The final fee is `1000.0 - 100.0 = 900.0`. The program prints `Total Before Discount: 1000.00`, `Discount: 100.00`, and `Final Fee: 900.00`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>arithmetic-operators</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>500
 2
@@ -7559,14 +6694,14 @@
 20</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>Total Before Discount: 1000.00
 Discount: 200.00
 Final Fee: 800.00</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>500
 2
@@ -7574,14 +6709,14 @@
 20</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Total Before Discount: 1000.00
 Discount: 0.00
 Final Fee: 1000.00</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>750
 1
@@ -7589,14 +6724,14 @@
 15</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Total Before Discount: 750.00
 Discount: 112.50
 Final Fee: 637.50</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>0
 1
@@ -7604,14 +6739,14 @@
 20</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Total Before Discount: 0.00
 Discount: 0.00
 Final Fee: 0.00</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>500
 0
@@ -7619,14 +6754,14 @@
 20</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>Total Before Discount: 0.00
 Discount: 0.00
 Final Fee: 0.00</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>500
 2
@@ -7634,14 +6769,14 @@
 0</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>Total Before Discount: 1000.00
 Discount: 0.00
 Final Fee: 1000.00</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>1000
 5
@@ -7649,540 +6784,517 @@
 100</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>Total Before Discount: 5000.00
 Discount: 5000.00
 Final Fee: 0.00</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>base_fee = float(input())
 years = int(input())
-is_student = int(input())
+is_student = int(input())          # 1 if the member is a student, else 0
 discount_percent = float(input())
-total = base_fee * years
-discount = total * discount_percent / 100 * is_student
-final_fee = total - discount
+total = base_fee * years                                 # fee before any discount
+discount = total * discount_percent / 100 * is_student    # multiplying by is_student zeroes it out for non-students
+final_fee = total - discount                              # payable amount after discount
 print(f"Total Before Discount: {total:.2f}")
 print(f"Discount: {discount:.2f}")
 print(f"Final Fee: {final_fee:.2f}")</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - Wallet Update</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A digital wallet app processes transactions in order: it starts from the user's opening balance, adds a top-up, then subtracts a purchase. The balance is updated in place using augmented assignment at each step.
 Write a program that reads the starting balance, the top-up amount, and the purchase amount, updates the balance with `balance += top_up` followed by `balance -= purchase`, and prints the final balance.
-### Input Format
-- Line 1: Starting balance
-- Line 2: Top-up amount
-- Line 3: Purchase amount
-### Output Format
-```
-125.0
-```
 ### Example Walkthrough
 In the sample, the balance starts at 100. Adding a top-up of 50 makes it 150, then subtracting a purchase of 25 makes it 125.0, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>assignment-operators</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>100
 50
 25</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>0
 10
 3</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>500
 0
 100</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>400.0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>1000
 250
 125</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>1125.0</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>-10
 20
 5</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>75.5
 4.5
 10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>1
 1
 2</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>b=float(input())
-b+=float(input())
-b-=float(input())
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>b=float(input())      # starting balance
+b+=float(input())     # add the top-up amount
+b-=float(input())     # subtract the purchase amount
 print(b)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - Gate Pass Boolean</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>A hostel's visitor gate pass system only issues a pass automatically when a visitor is an adult (18 years or older) AND has already paid the entry fee at the counter. The security guard's tablet reads both pieces of information and shows whether the pass should be granted.
 Write a program that reads the visitor's age and whether they have paid (`True` or `False`), then prints `True` if the visitor is 18 or older AND has paid, and `False` otherwise.
-### Input Format
-- Line 1: Age
-- Line 2: `True` or `False` indicating whether the visitor has paid
-### Output Format
-```
-True
-```
 ### Example Walkthrough
 In the sample, the age is 18 and paid is `True`. Since 18 is greater than or equal to 18 and the visitor has paid, both conditions are true, so the program prints `True`.
 ### Constraints
 - Age is a valid whole number in the ranges implied by the examples.
 - The paid input is always exactly `True` or `False`.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>comparison-and-logical-operators</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>18
 True</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>17
 True</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>20
 False</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>21
 True</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>0
 False</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>100
 True</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>18
 False</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>age=int(input())
-paid=input()=="True"
-print(age&gt;=18 and paid)</t>
+paid=input()=="True"    # compare the text input to "True" to get a real boolean
+print(age&gt;=18 and paid)  # logical AND: both conditions must be true</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Cast Sum Product</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>A calculator widget lets a user type two numbers into text boxes, but every value read from a text box arrives as a string. Before the widget can do any arithmetic, it must convert each entry to an integer.
 Write a program that reads two whole numbers (converting each from text to an integer), then prints their sum and product on separate lines in the form `Sum: &lt;value&gt;` and `Product: &lt;value&gt;`.
-### Input Format
-- Line 1: First number
-- Line 2: Second number
-### Output Format
-```
-Sum: 5
-Product: 6
-```
 ### Example Walkthrough
 In the sample, the numbers are 2 and 3. Converting both to integers and computing gives a sum of 2 + 3 = 5 and a product of 2 x 3 = 6, so the program prints `Sum: 5` and `Product: 6`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>data-types-and-operators</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>type-conversion</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>2
 3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>Sum: 5
 Product: 6</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>10
 5</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Sum: 15
 Product: 50</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>0
 7</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Sum: 7
 Product: 0</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>-2
 4</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Sum: 2
 Product: -8</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>100
 100</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>Sum: 200
 Product: 10000</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>1
 999</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>Sum: 1000
 Product: 999</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>-5
 -6</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>Sum: -11
 Product: 30</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>a=int(input())
-b=int(input())
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>a=int(input())   # convert text input to an integer
+b=int(input())   # convert text input to an integer
 print("Sum:", a+b)
 print("Product:", a*b)</t>
         </is>
